--- a/ЭДО/result.xlsx
+++ b/ЭДО/result.xlsx
@@ -903,7 +903,7 @@
     <row r="2" ht="12.95" customHeight="1">
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>ОТДЕЛЕНИЕ "БАНК ТАТАРСТАН" N8610 ПАО СБЕРБАНК</t>
+          <t>049205603</t>
         </is>
       </c>
       <c r="C2" s="45" t="n"/>

--- a/ЭДО/result.xlsx
+++ b/ЭДО/result.xlsx
@@ -903,7 +903,7 @@
     <row r="2" ht="12.95" customHeight="1">
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>049205603</t>
+          <t>ОТДЕЛЕНИЕ "БАНК ТАТАРСТАН" N8610 ПАО СБЕРБАНК</t>
         </is>
       </c>
       <c r="C2" s="45" t="n"/>
@@ -937,7 +937,11 @@
       <c r="AA2" s="47" t="n"/>
       <c r="AB2" s="47" t="n"/>
       <c r="AC2" s="48" t="n"/>
-      <c r="AD2" s="16" t="n"/>
+      <c r="AD2" s="16" t="inlineStr">
+        <is>
+          <t>049205603</t>
+        </is>
+      </c>
       <c r="AE2" s="45" t="n"/>
       <c r="AF2" s="45" t="n"/>
       <c r="AG2" s="45" t="n"/>
@@ -966,7 +970,11 @@
       <c r="AA3" s="45" t="n"/>
       <c r="AB3" s="45" t="n"/>
       <c r="AC3" s="46" t="n"/>
-      <c r="AD3" s="52" t="n"/>
+      <c r="AD3" s="52" t="inlineStr">
+        <is>
+          <t>40502810362210100004</t>
+        </is>
+      </c>
       <c r="AR3" s="50" t="n"/>
     </row>
     <row r="4" ht="11.1" customHeight="1">
@@ -1059,7 +1067,11 @@
       <c r="AA5" s="45" t="n"/>
       <c r="AB5" s="45" t="n"/>
       <c r="AC5" s="46" t="n"/>
-      <c r="AD5" s="51" t="n"/>
+      <c r="AD5" s="51" t="inlineStr">
+        <is>
+          <t>30101810600000000603</t>
+        </is>
+      </c>
       <c r="AE5" s="45" t="n"/>
       <c r="AF5" s="45" t="n"/>
       <c r="AG5" s="45" t="n"/>
@@ -1076,7 +1088,11 @@
       <c r="AR5" s="46" t="n"/>
     </row>
     <row r="6" ht="11.1" customHeight="1">
-      <c r="B6" s="26" t="n"/>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Филиал ФГУП "Охрана" Росгвардии по Республике Татарстан</t>
+        </is>
+      </c>
       <c r="C6" s="45" t="n"/>
       <c r="D6" s="45" t="n"/>
       <c r="E6" s="45" t="n"/>
@@ -1162,7 +1178,7 @@
     <row r="10" ht="11.1" customHeight="1">
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>Счет на оплату № 8  от 01       20   г.</t>
+          <t>Счет на оплату №16-187923 от 15.12.2020  г.</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1236,11 @@
 (Исполнитель):</t>
         </is>
       </c>
-      <c r="G14" s="32" t="n"/>
+      <c r="G14" s="32" t="inlineStr">
+        <is>
+          <t>Филиал ФГУП "Охрана" Росгвардии по Республике Татарстан,127473, Москва г, Делегатская ул, дом 5, строение 1</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="11.1" customFormat="1" customHeight="1" s="1"/>
     <row r="16" ht="6.95" customFormat="1" customHeight="1" s="1"/>
@@ -1231,7 +1251,11 @@
 (Заказчик):</t>
         </is>
       </c>
-      <c r="G17" s="32" t="n"/>
+      <c r="G17" s="32" t="inlineStr">
+        <is>
+          <t>ООО "ЭСПЕРАНС",119049, РФ, г.Москва, 1-й Добрынинский пер.,д.19, стр.6, пом.III, комната 1, этаж 1</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="11.1" customFormat="1" customHeight="1" s="1"/>
     <row r="19" ht="6.95" customFormat="1" customHeight="1" s="1"/>
@@ -1241,7 +1265,11 @@
           <t>Основание:</t>
         </is>
       </c>
-      <c r="G20" s="32" t="n"/>
+      <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t>№113/4 от 01.09.2013 (новый перечень от 01.01.2019)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="6.95" customFormat="1" customHeight="1" s="1"/>
     <row r="22" ht="12.95" customHeight="1">

--- a/ЭДО/result.xlsx
+++ b/ЭДО/result.xlsx
@@ -52,7 +52,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -259,7 +259,22 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -268,7 +283,9 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -281,7 +298,42 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -317,33 +369,78 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -351,136 +448,136 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -493,9 +590,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -866,37 +980,37 @@
   <dimension ref="B2:AR37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1"/>
   <cols>
-    <col width="1.1640625" customWidth="1" style="1" min="1" max="1"/>
-    <col width="3.5" customWidth="1" style="1" min="2" max="2"/>
-    <col width="1.83203125" customWidth="1" style="1" min="3" max="3"/>
-    <col width="1.6640625" customWidth="1" style="1" min="4" max="4"/>
-    <col width="3.5" customWidth="1" style="1" min="5" max="5"/>
-    <col width="4.33203125" customWidth="1" style="1" min="6" max="6"/>
-    <col width="2.5" customWidth="1" style="1" min="7" max="7"/>
-    <col width="0.5" customWidth="1" style="1" min="8" max="8"/>
-    <col width="3" customWidth="1" style="1" min="9" max="9"/>
-    <col width="3.5" customWidth="1" style="1" min="10" max="16"/>
-    <col width="2.83203125" customWidth="1" style="1" min="17" max="17"/>
-    <col width="1.33203125" customWidth="1" style="1" min="18" max="19"/>
-    <col width="2.83203125" customWidth="1" style="1" min="20" max="21"/>
-    <col width="2.1640625" customWidth="1" style="1" min="22" max="22"/>
-    <col width="1.33203125" customWidth="1" style="1" min="23" max="23"/>
-    <col width="0.1640625" customWidth="1" style="1" min="24" max="24"/>
-    <col width="3.33203125" customWidth="1" style="1" min="25" max="25"/>
-    <col width="2.1640625" customWidth="1" style="1" min="26" max="26"/>
-    <col width="1.33203125" customWidth="1" style="1" min="27" max="27"/>
-    <col width="2.1640625" customWidth="1" style="1" min="28" max="28"/>
-    <col width="1.33203125" customWidth="1" style="1" min="29" max="29"/>
-    <col width="4" customWidth="1" style="1" min="30" max="30"/>
-    <col width="1.83203125" customWidth="1" style="1" min="31" max="32"/>
-    <col width="3.5" customWidth="1" style="1" min="33" max="35"/>
-    <col width="2.1640625" customWidth="1" style="1" min="36" max="36"/>
-    <col width="0.33203125" customWidth="1" style="1" min="37" max="37"/>
-    <col width="1" customWidth="1" style="1" min="38" max="38"/>
-    <col width="3.5" customWidth="1" style="1" min="39" max="42"/>
-    <col width="1.33203125" customWidth="1" style="1" min="43" max="43"/>
-    <col width="0.6640625" customWidth="1" style="1" min="44" max="44"/>
-    <col width="2.1640625" customWidth="1" style="1" min="45" max="45"/>
+    <col width="1.1640625" customWidth="1" style="35" min="1" max="1"/>
+    <col width="3.5" customWidth="1" style="35" min="2" max="2"/>
+    <col width="1.83203125" customWidth="1" style="35" min="3" max="3"/>
+    <col width="1.6640625" customWidth="1" style="35" min="4" max="4"/>
+    <col width="3.5" customWidth="1" style="35" min="5" max="5"/>
+    <col width="4.33203125" customWidth="1" style="35" min="6" max="6"/>
+    <col width="2.5" customWidth="1" style="35" min="7" max="7"/>
+    <col width="0.5" customWidth="1" style="35" min="8" max="8"/>
+    <col width="3" customWidth="1" style="35" min="9" max="9"/>
+    <col width="3.5" customWidth="1" style="35" min="10" max="16"/>
+    <col width="2.83203125" customWidth="1" style="35" min="17" max="17"/>
+    <col width="1.33203125" customWidth="1" style="35" min="18" max="19"/>
+    <col width="2.83203125" customWidth="1" style="35" min="20" max="21"/>
+    <col width="2.1640625" customWidth="1" style="35" min="22" max="22"/>
+    <col width="1.33203125" customWidth="1" style="35" min="23" max="23"/>
+    <col width="0.1640625" customWidth="1" style="35" min="24" max="24"/>
+    <col width="3.33203125" customWidth="1" style="35" min="25" max="25"/>
+    <col width="2.1640625" customWidth="1" style="35" min="26" max="26"/>
+    <col width="1.33203125" customWidth="1" style="35" min="27" max="27"/>
+    <col width="2.1640625" customWidth="1" style="35" min="28" max="28"/>
+    <col width="1.33203125" customWidth="1" style="35" min="29" max="29"/>
+    <col width="4" customWidth="1" style="35" min="30" max="30"/>
+    <col width="1.83203125" customWidth="1" style="35" min="31" max="32"/>
+    <col width="3.5" customWidth="1" style="35" min="33" max="35"/>
+    <col width="2.1640625" customWidth="1" style="35" min="36" max="36"/>
+    <col width="0.33203125" customWidth="1" style="35" min="37" max="37"/>
+    <col width="1" customWidth="1" style="35" min="38" max="38"/>
+    <col width="3.5" customWidth="1" style="35" min="39" max="42"/>
+    <col width="1.33203125" customWidth="1" style="35" min="43" max="43"/>
+    <col width="0.6640625" customWidth="1" style="35" min="44" max="44"/>
+    <col width="2.1640625" customWidth="1" style="35" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="11.1" customHeight="1"/>
@@ -927,7 +1041,7 @@
       <c r="U2" s="45" t="n"/>
       <c r="V2" s="45" t="n"/>
       <c r="W2" s="46" t="n"/>
-      <c r="X2" s="15" t="inlineStr">
+      <c r="X2" s="31" t="inlineStr">
         <is>
           <t>БИК</t>
         </is>
@@ -937,7 +1051,7 @@
       <c r="AA2" s="47" t="n"/>
       <c r="AB2" s="47" t="n"/>
       <c r="AC2" s="48" t="n"/>
-      <c r="AD2" s="16" t="inlineStr">
+      <c r="AD2" s="32" t="inlineStr">
         <is>
           <t>049205603</t>
         </is>
@@ -978,7 +1092,7 @@
       <c r="AR3" s="50" t="n"/>
     </row>
     <row r="4" ht="11.1" customHeight="1">
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Банк получателя</t>
         </is>
@@ -1027,14 +1141,14 @@
       <c r="AR4" s="54" t="n"/>
     </row>
     <row r="5" ht="12.95" customHeight="1">
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>ИНН</t>
         </is>
       </c>
       <c r="C5" s="45" t="n"/>
       <c r="D5" s="45" t="n"/>
-      <c r="E5" s="31" t="n"/>
+      <c r="E5" s="28" t="n"/>
       <c r="F5" s="45" t="n"/>
       <c r="G5" s="45" t="n"/>
       <c r="H5" s="45" t="n"/>
@@ -1042,13 +1156,13 @@
       <c r="J5" s="45" t="n"/>
       <c r="K5" s="45" t="n"/>
       <c r="L5" s="46" t="n"/>
-      <c r="M5" s="30" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>КПП</t>
         </is>
       </c>
       <c r="N5" s="45" t="n"/>
-      <c r="O5" s="31" t="n"/>
+      <c r="O5" s="28" t="n"/>
       <c r="P5" s="45" t="n"/>
       <c r="Q5" s="45" t="n"/>
       <c r="R5" s="45" t="n"/>
@@ -1088,7 +1202,7 @@
       <c r="AR5" s="46" t="n"/>
     </row>
     <row r="6" ht="11.1" customHeight="1">
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Филиал ФГУП "Охрана" Росгвардии по Республике Татарстан</t>
         </is>
@@ -1127,7 +1241,7 @@
       <c r="AR7" s="50" t="n"/>
     </row>
     <row r="8" ht="11.1" customHeight="1">
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
@@ -1176,15 +1290,15 @@
       <c r="AR8" s="54" t="n"/>
     </row>
     <row r="10" ht="11.1" customHeight="1">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Счет на оплату №16-187923 от 15.12.2020  г.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="11.1" customHeight="1"/>
-    <row r="12" ht="6.95" customFormat="1" customHeight="1" s="1">
-      <c r="B12" s="29" t="n"/>
+    <row r="12" ht="6.95" customFormat="1" customHeight="1" s="35">
+      <c r="B12" s="26" t="n"/>
       <c r="C12" s="56" t="n"/>
       <c r="D12" s="56" t="n"/>
       <c r="E12" s="56" t="n"/>
@@ -1228,58 +1342,58 @@
       <c r="AQ12" s="56" t="n"/>
       <c r="AR12" s="56" t="n"/>
     </row>
-    <row r="13" ht="6.95" customFormat="1" customHeight="1" s="1"/>
+    <row r="13" ht="6.95" customFormat="1" customHeight="1" s="35"/>
     <row r="14" ht="14.1" customHeight="1">
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Поставщик
 (Исполнитель):</t>
         </is>
       </c>
-      <c r="G14" s="32" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Филиал ФГУП "Охрана" Росгвардии по Республике Татарстан,127473, Москва г, Делегатская ул, дом 5, строение 1</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="11.1" customFormat="1" customHeight="1" s="1"/>
-    <row r="16" ht="6.95" customFormat="1" customHeight="1" s="1"/>
+    <row r="15" ht="11.1" customFormat="1" customHeight="1" s="35"/>
+    <row r="16" ht="6.95" customFormat="1" customHeight="1" s="35"/>
     <row r="17" ht="14.1" customHeight="1">
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Покупатель
 (Заказчик):</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>ООО "ЭСПЕРАНС",119049, РФ, г.Москва, 1-й Добрынинский пер.,д.19, стр.6, пом.III, комната 1, этаж 1</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="11.1" customFormat="1" customHeight="1" s="1"/>
-    <row r="19" ht="6.95" customFormat="1" customHeight="1" s="1"/>
+    <row r="18" ht="11.1" customFormat="1" customHeight="1" s="35"/>
+    <row r="19" ht="6.95" customFormat="1" customHeight="1" s="35"/>
     <row r="20" ht="12.95" customHeight="1">
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Основание:</t>
         </is>
       </c>
-      <c r="G20" s="32" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>№113/4 от 01.09.2013 (новый перечень от 01.01.2019)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="6.95" customFormat="1" customHeight="1" s="1"/>
+    <row r="21" ht="6.95" customFormat="1" customHeight="1" s="35"/>
     <row r="22" ht="12.95" customHeight="1">
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
       <c r="C22" s="57" t="n"/>
-      <c r="D22" s="39" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Товары (работы, услуги)</t>
         </is>
@@ -1304,7 +1418,7 @@
       <c r="V22" s="57" t="n"/>
       <c r="W22" s="57" t="n"/>
       <c r="X22" s="57" t="n"/>
-      <c r="Y22" s="39" t="inlineStr">
+      <c r="Y22" s="13" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
@@ -1312,14 +1426,14 @@
       <c r="Z22" s="57" t="n"/>
       <c r="AA22" s="57" t="n"/>
       <c r="AB22" s="57" t="n"/>
-      <c r="AC22" s="39" t="inlineStr">
+      <c r="AC22" s="13" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
       <c r="AD22" s="57" t="n"/>
       <c r="AE22" s="57" t="n"/>
-      <c r="AF22" s="39" t="inlineStr">
+      <c r="AF22" s="13" t="inlineStr">
         <is>
           <t>Цена</t>
         </is>
@@ -1328,7 +1442,7 @@
       <c r="AH22" s="57" t="n"/>
       <c r="AI22" s="57" t="n"/>
       <c r="AJ22" s="57" t="n"/>
-      <c r="AK22" s="33" t="inlineStr">
+      <c r="AK22" s="11" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
@@ -1340,250 +1454,260 @@
       <c r="AP22" s="57" t="n"/>
       <c r="AQ22" s="58" t="n"/>
     </row>
-    <row r="23" ht="44.1" customHeight="1">
-      <c r="B23" s="34" t="n">
+    <row r="23" ht="50" customHeight="1">
+      <c r="B23" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="45" t="n"/>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="45" t="n"/>
-      <c r="F23" s="45" t="n"/>
-      <c r="G23" s="45" t="n"/>
-      <c r="H23" s="45" t="n"/>
-      <c r="I23" s="45" t="n"/>
-      <c r="J23" s="45" t="n"/>
-      <c r="K23" s="45" t="n"/>
-      <c r="L23" s="45" t="n"/>
-      <c r="M23" s="45" t="n"/>
-      <c r="N23" s="45" t="n"/>
-      <c r="O23" s="45" t="n"/>
-      <c r="P23" s="45" t="n"/>
-      <c r="Q23" s="45" t="n"/>
-      <c r="R23" s="45" t="n"/>
-      <c r="S23" s="45" t="n"/>
-      <c r="T23" s="45" t="n"/>
-      <c r="U23" s="45" t="n"/>
-      <c r="V23" s="45" t="n"/>
-      <c r="W23" s="45" t="n"/>
-      <c r="X23" s="45" t="n"/>
-      <c r="Y23" s="3" t="n"/>
-      <c r="Z23" s="4" t="n"/>
-      <c r="AA23" s="4" t="n"/>
-      <c r="AB23" s="4" t="n"/>
-      <c r="AC23" s="5" t="n"/>
-      <c r="AD23" s="6" t="n"/>
-      <c r="AE23" s="6" t="n"/>
-      <c r="AF23" s="36" t="n"/>
-      <c r="AG23" s="45" t="n"/>
-      <c r="AH23" s="45" t="n"/>
-      <c r="AI23" s="45" t="n"/>
-      <c r="AJ23" s="45" t="n"/>
-      <c r="AK23" s="37" t="n"/>
-      <c r="AL23" s="45" t="n"/>
-      <c r="AM23" s="45" t="n"/>
-      <c r="AN23" s="45" t="n"/>
-      <c r="AO23" s="45" t="n"/>
-      <c r="AP23" s="45" t="n"/>
-      <c r="AQ23" s="59" t="n"/>
-    </row>
-    <row r="24" ht="6.95" customFormat="1" customHeight="1" s="1">
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="7" t="n"/>
-      <c r="P24" s="7" t="n"/>
-      <c r="Q24" s="7" t="n"/>
-      <c r="R24" s="7" t="n"/>
-      <c r="S24" s="7" t="n"/>
-      <c r="T24" s="7" t="n"/>
-      <c r="U24" s="7" t="n"/>
-      <c r="V24" s="7" t="n"/>
-      <c r="W24" s="7" t="n"/>
-      <c r="X24" s="7" t="n"/>
-      <c r="Y24" s="7" t="n"/>
-      <c r="Z24" s="7" t="n"/>
-      <c r="AA24" s="7" t="n"/>
-      <c r="AB24" s="7" t="n"/>
-      <c r="AC24" s="7" t="n"/>
-      <c r="AD24" s="7" t="n"/>
-      <c r="AE24" s="7" t="n"/>
-      <c r="AF24" s="7" t="n"/>
-      <c r="AG24" s="7" t="n"/>
-      <c r="AH24" s="7" t="n"/>
-      <c r="AI24" s="7" t="n"/>
-      <c r="AJ24" s="7" t="n"/>
-      <c r="AK24" s="7" t="n"/>
-      <c r="AL24" s="7" t="n"/>
-      <c r="AM24" s="7" t="n"/>
-      <c r="AN24" s="7" t="n"/>
-      <c r="AO24" s="7" t="n"/>
-      <c r="AP24" s="7" t="n"/>
-      <c r="AQ24" s="7" t="n"/>
+      <c r="C23" s="60" t="n"/>
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>Оказание услуг по техническому обслуживанию технических средств охраны</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="n"/>
+      <c r="F23" s="60" t="n"/>
+      <c r="G23" s="60" t="n"/>
+      <c r="H23" s="60" t="n"/>
+      <c r="I23" s="60" t="n"/>
+      <c r="J23" s="60" t="n"/>
+      <c r="K23" s="60" t="n"/>
+      <c r="L23" s="60" t="n"/>
+      <c r="M23" s="60" t="n"/>
+      <c r="N23" s="60" t="n"/>
+      <c r="O23" s="60" t="n"/>
+      <c r="P23" s="60" t="n"/>
+      <c r="Q23" s="60" t="n"/>
+      <c r="R23" s="60" t="n"/>
+      <c r="S23" s="60" t="n"/>
+      <c r="T23" s="60" t="n"/>
+      <c r="U23" s="60" t="n"/>
+      <c r="V23" s="60" t="n"/>
+      <c r="W23" s="60" t="n"/>
+      <c r="X23" s="60" t="n"/>
+      <c r="Y23" s="60" t="n"/>
+      <c r="Z23" s="60" t="n"/>
+      <c r="AA23" s="60" t="n"/>
+      <c r="AB23" s="60" t="n"/>
+      <c r="AC23" s="60" t="n"/>
+      <c r="AD23" s="60" t="n"/>
+      <c r="AE23" s="60" t="n"/>
+      <c r="AF23" s="61" t="n"/>
+      <c r="AG23" s="60" t="n"/>
+      <c r="AH23" s="60" t="n"/>
+      <c r="AI23" s="60" t="n"/>
+      <c r="AJ23" s="60" t="n"/>
+      <c r="AK23" s="61" t="n"/>
+      <c r="AL23" s="60" t="n"/>
+      <c r="AM23" s="60" t="n"/>
+      <c r="AN23" s="60" t="n"/>
+      <c r="AO23" s="60" t="n"/>
+      <c r="AP23" s="60" t="n"/>
+      <c r="AQ23" s="62" t="n"/>
+    </row>
+    <row r="24" ht="50" customFormat="1" customHeight="1" s="35">
+      <c r="B24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="64" t="n"/>
+      <c r="D24" s="64" t="inlineStr">
+        <is>
+          <t>Сосание хуев</t>
+        </is>
+      </c>
+      <c r="E24" s="64" t="n"/>
+      <c r="F24" s="64" t="n"/>
+      <c r="G24" s="64" t="n"/>
+      <c r="H24" s="64" t="n"/>
+      <c r="I24" s="64" t="n"/>
+      <c r="J24" s="64" t="n"/>
+      <c r="K24" s="64" t="n"/>
+      <c r="L24" s="64" t="n"/>
+      <c r="M24" s="64" t="n"/>
+      <c r="N24" s="64" t="n"/>
+      <c r="O24" s="64" t="n"/>
+      <c r="P24" s="64" t="n"/>
+      <c r="Q24" s="64" t="n"/>
+      <c r="R24" s="64" t="n"/>
+      <c r="S24" s="64" t="n"/>
+      <c r="T24" s="64" t="n"/>
+      <c r="U24" s="64" t="n"/>
+      <c r="V24" s="64" t="n"/>
+      <c r="W24" s="64" t="n"/>
+      <c r="X24" s="64" t="n"/>
+      <c r="Y24" s="64" t="n"/>
+      <c r="Z24" s="64" t="n"/>
+      <c r="AA24" s="64" t="n"/>
+      <c r="AB24" s="64" t="n"/>
+      <c r="AC24" s="64" t="n"/>
+      <c r="AD24" s="64" t="n"/>
+      <c r="AE24" s="64" t="n"/>
+      <c r="AF24" s="64" t="n"/>
+      <c r="AG24" s="64" t="n"/>
+      <c r="AH24" s="64" t="n"/>
+      <c r="AI24" s="64" t="n"/>
+      <c r="AJ24" s="64" t="n"/>
+      <c r="AK24" s="64" t="n"/>
+      <c r="AL24" s="64" t="n"/>
+      <c r="AM24" s="64" t="n"/>
+      <c r="AN24" s="64" t="n"/>
+      <c r="AO24" s="64" t="n"/>
+      <c r="AP24" s="64" t="n"/>
+      <c r="AQ24" s="63" t="n"/>
     </row>
     <row r="25" ht="12.95" customHeight="1">
-      <c r="AA25" s="8" t="n"/>
-      <c r="AB25" s="8" t="n"/>
-      <c r="AC25" s="8" t="n"/>
-      <c r="AD25" s="8" t="n"/>
-      <c r="AE25" s="8" t="n"/>
-      <c r="AF25" s="8" t="n"/>
-      <c r="AG25" s="8" t="n"/>
-      <c r="AH25" s="8" t="n"/>
-      <c r="AI25" s="8" t="n"/>
-      <c r="AJ25" s="8" t="n"/>
-      <c r="AK25" s="8" t="inlineStr">
+      <c r="AA25" s="3" t="n"/>
+      <c r="AB25" s="3" t="n"/>
+      <c r="AC25" s="3" t="n"/>
+      <c r="AD25" s="3" t="n"/>
+      <c r="AE25" s="3" t="n"/>
+      <c r="AF25" s="3" t="n"/>
+      <c r="AG25" s="3" t="n"/>
+      <c r="AH25" s="3" t="n"/>
+      <c r="AI25" s="3" t="n"/>
+      <c r="AJ25" s="3" t="n"/>
+      <c r="AK25" s="3" t="inlineStr">
         <is>
           <t>Итого:</t>
         </is>
       </c>
-      <c r="AL25" s="40" t="n"/>
+      <c r="AL25" s="8" t="n"/>
     </row>
     <row r="26" ht="12.95" customHeight="1">
-      <c r="AA26" s="8" t="n"/>
-      <c r="AB26" s="8" t="n"/>
-      <c r="AC26" s="8" t="n"/>
-      <c r="AD26" s="8" t="n"/>
-      <c r="AE26" s="8" t="n"/>
-      <c r="AF26" s="8" t="n"/>
-      <c r="AG26" s="8" t="n"/>
-      <c r="AH26" s="8" t="n"/>
-      <c r="AI26" s="8" t="n"/>
-      <c r="AJ26" s="8" t="n"/>
-      <c r="AK26" s="8" t="inlineStr">
+      <c r="AA26" s="3" t="n"/>
+      <c r="AB26" s="3" t="n"/>
+      <c r="AC26" s="3" t="n"/>
+      <c r="AD26" s="3" t="n"/>
+      <c r="AE26" s="3" t="n"/>
+      <c r="AF26" s="3" t="n"/>
+      <c r="AG26" s="3" t="n"/>
+      <c r="AH26" s="3" t="n"/>
+      <c r="AI26" s="3" t="n"/>
+      <c r="AJ26" s="3" t="n"/>
+      <c r="AK26" s="3" t="inlineStr">
         <is>
           <t>В том числе НДС:</t>
         </is>
       </c>
-      <c r="AL26" s="40" t="n"/>
+      <c r="AL26" s="8" t="n"/>
     </row>
     <row r="27" ht="12.95" customHeight="1">
-      <c r="AA27" s="8" t="n"/>
-      <c r="AB27" s="8" t="n"/>
-      <c r="AC27" s="8" t="n"/>
-      <c r="AD27" s="8" t="n"/>
-      <c r="AE27" s="8" t="n"/>
-      <c r="AF27" s="8" t="n"/>
-      <c r="AG27" s="8" t="n"/>
-      <c r="AH27" s="8" t="n"/>
-      <c r="AI27" s="8" t="n"/>
-      <c r="AJ27" s="8" t="n"/>
-      <c r="AK27" s="8" t="inlineStr">
+      <c r="AA27" s="3" t="n"/>
+      <c r="AB27" s="3" t="n"/>
+      <c r="AC27" s="3" t="n"/>
+      <c r="AD27" s="3" t="n"/>
+      <c r="AE27" s="3" t="n"/>
+      <c r="AF27" s="3" t="n"/>
+      <c r="AG27" s="3" t="n"/>
+      <c r="AH27" s="3" t="n"/>
+      <c r="AI27" s="3" t="n"/>
+      <c r="AJ27" s="3" t="n"/>
+      <c r="AK27" s="3" t="inlineStr">
         <is>
           <t>Всего к оплате:</t>
         </is>
       </c>
-      <c r="AL27" s="40" t="n"/>
+      <c r="AL27" s="8" t="n"/>
     </row>
     <row r="28" ht="12.95" customHeight="1">
-      <c r="B28" s="41" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Всего наименований  , на сумму                  руб.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="12.95" customHeight="1">
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Два миллиона пятьсот тысяч рублей 00 копеек</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="6.95" customFormat="1" customHeight="1" s="1"/>
-    <row r="31" ht="12" customFormat="1" customHeight="1" s="1">
-      <c r="B31" s="42" t="inlineStr">
+    <row r="30" ht="6.95" customFormat="1" customHeight="1" s="35"/>
+    <row r="31" ht="12" customFormat="1" customHeight="1" s="35">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Внимание!</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="12" customFormat="1" customHeight="1" s="1">
-      <c r="B32" s="42" t="inlineStr">
+    <row r="32" ht="12" customFormat="1" customHeight="1" s="35">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Оплата данного счета означает согласие с условиями поставки товара.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="12" customFormat="1" customHeight="1" s="1">
-      <c r="B33" s="42" t="inlineStr">
+    <row r="33" ht="12" customFormat="1" customHeight="1" s="35">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Уведомление об оплате обязательно, в противном случае не гарантируется наличие товара на складе.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="B34" s="42" t="inlineStr">
+    <row r="34" ht="24" customFormat="1" customHeight="1" s="35">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Товар отпускается по факту прихода денег на р/с Поставщика, самовывозом, при наличии доверенности и паспорта.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="6.95" customFormat="1" customHeight="1" s="1">
-      <c r="B35" s="29" t="n"/>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="29" t="n"/>
-      <c r="E35" s="29" t="n"/>
-      <c r="F35" s="29" t="n"/>
-      <c r="G35" s="29" t="n"/>
-      <c r="H35" s="29" t="n"/>
-      <c r="I35" s="29" t="n"/>
-      <c r="J35" s="29" t="n"/>
-      <c r="K35" s="29" t="n"/>
-      <c r="L35" s="29" t="n"/>
-      <c r="M35" s="29" t="n"/>
-      <c r="N35" s="29" t="n"/>
-      <c r="O35" s="29" t="n"/>
-      <c r="P35" s="29" t="n"/>
-      <c r="Q35" s="29" t="n"/>
-      <c r="R35" s="29" t="n"/>
-      <c r="S35" s="29" t="n"/>
-      <c r="T35" s="29" t="n"/>
-      <c r="U35" s="29" t="n"/>
-      <c r="V35" s="29" t="n"/>
-      <c r="W35" s="29" t="n"/>
-      <c r="X35" s="29" t="n"/>
-      <c r="Y35" s="29" t="n"/>
-      <c r="Z35" s="29" t="n"/>
-      <c r="AA35" s="29" t="n"/>
-      <c r="AB35" s="29" t="n"/>
-      <c r="AC35" s="29" t="n"/>
-      <c r="AD35" s="29" t="n"/>
-      <c r="AE35" s="29" t="n"/>
-      <c r="AF35" s="29" t="n"/>
-      <c r="AG35" s="29" t="n"/>
-      <c r="AH35" s="29" t="n"/>
-      <c r="AI35" s="29" t="n"/>
-      <c r="AJ35" s="29" t="n"/>
-      <c r="AK35" s="29" t="n"/>
-      <c r="AL35" s="29" t="n"/>
-      <c r="AM35" s="29" t="n"/>
-      <c r="AN35" s="29" t="n"/>
-      <c r="AO35" s="29" t="n"/>
-      <c r="AP35" s="29" t="n"/>
-      <c r="AQ35" s="29" t="n"/>
-      <c r="AR35" s="29" t="n"/>
+    <row r="35" ht="6.95" customFormat="1" customHeight="1" s="35">
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="26" t="n"/>
+      <c r="G35" s="26" t="n"/>
+      <c r="H35" s="26" t="n"/>
+      <c r="I35" s="26" t="n"/>
+      <c r="J35" s="26" t="n"/>
+      <c r="K35" s="26" t="n"/>
+      <c r="L35" s="26" t="n"/>
+      <c r="M35" s="26" t="n"/>
+      <c r="N35" s="26" t="n"/>
+      <c r="O35" s="26" t="n"/>
+      <c r="P35" s="26" t="n"/>
+      <c r="Q35" s="26" t="n"/>
+      <c r="R35" s="26" t="n"/>
+      <c r="S35" s="26" t="n"/>
+      <c r="T35" s="26" t="n"/>
+      <c r="U35" s="26" t="n"/>
+      <c r="V35" s="26" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="26" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="26" t="n"/>
+      <c r="AB35" s="26" t="n"/>
+      <c r="AC35" s="26" t="n"/>
+      <c r="AD35" s="26" t="n"/>
+      <c r="AE35" s="26" t="n"/>
+      <c r="AF35" s="26" t="n"/>
+      <c r="AG35" s="26" t="n"/>
+      <c r="AH35" s="26" t="n"/>
+      <c r="AI35" s="26" t="n"/>
+      <c r="AJ35" s="26" t="n"/>
+      <c r="AK35" s="26" t="n"/>
+      <c r="AL35" s="26" t="n"/>
+      <c r="AM35" s="26" t="n"/>
+      <c r="AN35" s="26" t="n"/>
+      <c r="AO35" s="26" t="n"/>
+      <c r="AP35" s="26" t="n"/>
+      <c r="AQ35" s="26" t="n"/>
+      <c r="AR35" s="26" t="n"/>
     </row>
     <row r="37" ht="12.95" customHeight="1">
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Руководитель</t>
         </is>
       </c>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="43" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="7" t="n"/>
       <c r="N37" s="53" t="n"/>
       <c r="O37" s="53" t="n"/>
       <c r="P37" s="53" t="n"/>
@@ -1594,16 +1718,16 @@
       <c r="U37" s="53" t="n"/>
       <c r="V37" s="53" t="n"/>
       <c r="W37" s="53" t="n"/>
-      <c r="Z37" s="9" t="inlineStr">
+      <c r="Z37" s="4" t="inlineStr">
         <is>
           <t>Бухгалтер</t>
         </is>
       </c>
-      <c r="AA37" s="9" t="n"/>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="43" t="n"/>
+      <c r="AA37" s="4" t="n"/>
+      <c r="AG37" s="5" t="n"/>
+      <c r="AH37" s="5" t="n"/>
+      <c r="AI37" s="5" t="n"/>
+      <c r="AJ37" s="7" t="n"/>
       <c r="AK37" s="53" t="n"/>
       <c r="AL37" s="53" t="n"/>
       <c r="AM37" s="53" t="n"/>
@@ -1615,18 +1739,29 @@
     </row>
     <row r="38" ht="11.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="B31:AR31"/>
-    <mergeCell ref="B32:AR32"/>
-    <mergeCell ref="B33:AR33"/>
-    <mergeCell ref="B34:AR34"/>
-    <mergeCell ref="M37:W37"/>
-    <mergeCell ref="AJ37:AR37"/>
-    <mergeCell ref="AL25:AQ25"/>
-    <mergeCell ref="AL26:AQ26"/>
-    <mergeCell ref="AL27:AQ27"/>
-    <mergeCell ref="B28:AR28"/>
-    <mergeCell ref="B29:AP29"/>
+  <mergeCells count="51">
+    <mergeCell ref="B2:W3"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AD2:AR2"/>
+    <mergeCell ref="X3:AC4"/>
+    <mergeCell ref="AD3:AR4"/>
+    <mergeCell ref="B4:W4"/>
+    <mergeCell ref="AD5:AR8"/>
+    <mergeCell ref="B6:W7"/>
+    <mergeCell ref="B8:W8"/>
+    <mergeCell ref="B10:AR11"/>
+    <mergeCell ref="B12:AR12"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:W5"/>
+    <mergeCell ref="X5:AC8"/>
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="G14:AR15"/>
+    <mergeCell ref="B17:F18"/>
+    <mergeCell ref="G17:AR18"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G20:AR20"/>
     <mergeCell ref="AK22:AQ22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:X23"/>
@@ -1637,28 +1772,25 @@
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="AF22:AJ22"/>
-    <mergeCell ref="B14:F15"/>
-    <mergeCell ref="G14:AR15"/>
-    <mergeCell ref="B17:F18"/>
-    <mergeCell ref="G17:AR18"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G20:AR20"/>
-    <mergeCell ref="AD5:AR8"/>
-    <mergeCell ref="B6:W7"/>
-    <mergeCell ref="B8:W8"/>
-    <mergeCell ref="B10:AR11"/>
-    <mergeCell ref="B12:AR12"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:W5"/>
-    <mergeCell ref="X5:AC8"/>
-    <mergeCell ref="B2:W3"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AD2:AR2"/>
-    <mergeCell ref="X3:AC4"/>
-    <mergeCell ref="AD3:AR4"/>
-    <mergeCell ref="B4:W4"/>
+    <mergeCell ref="AL25:AQ25"/>
+    <mergeCell ref="AL26:AQ26"/>
+    <mergeCell ref="AL27:AQ27"/>
+    <mergeCell ref="B28:AR28"/>
+    <mergeCell ref="B29:AP29"/>
+    <mergeCell ref="B31:AR31"/>
+    <mergeCell ref="B32:AR32"/>
+    <mergeCell ref="B33:AR33"/>
+    <mergeCell ref="B34:AR34"/>
+    <mergeCell ref="M37:W37"/>
+    <mergeCell ref="AJ37:AR37"/>
+    <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:X24"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF24:AJ24"/>
+    <mergeCell ref="AK24:AQ24"/>
   </mergeCells>
   <pageMargins left="0.75" right="1" top="0.75" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ЭДО/result.xlsx
+++ b/ЭДО/result.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Arial"/>
       <sz val="8"/>
@@ -43,6 +43,19 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -52,7 +65,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -306,7 +319,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
@@ -318,41 +342,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -381,6 +370,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -433,6 +446,16 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -440,144 +463,143 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -590,8 +612,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -609,6 +631,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -977,775 +1024,972 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="B2:AR37"/>
+  <dimension ref="A2:AT38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1"/>
   <cols>
-    <col width="1.1640625" customWidth="1" style="35" min="1" max="1"/>
-    <col width="3.5" customWidth="1" style="35" min="2" max="2"/>
-    <col width="1.83203125" customWidth="1" style="35" min="3" max="3"/>
-    <col width="1.6640625" customWidth="1" style="35" min="4" max="4"/>
-    <col width="3.5" customWidth="1" style="35" min="5" max="5"/>
-    <col width="4.33203125" customWidth="1" style="35" min="6" max="6"/>
-    <col width="2.5" customWidth="1" style="35" min="7" max="7"/>
-    <col width="0.5" customWidth="1" style="35" min="8" max="8"/>
-    <col width="3" customWidth="1" style="35" min="9" max="9"/>
-    <col width="3.5" customWidth="1" style="35" min="10" max="16"/>
-    <col width="2.83203125" customWidth="1" style="35" min="17" max="17"/>
-    <col width="1.33203125" customWidth="1" style="35" min="18" max="19"/>
-    <col width="2.83203125" customWidth="1" style="35" min="20" max="21"/>
-    <col width="2.1640625" customWidth="1" style="35" min="22" max="22"/>
-    <col width="1.33203125" customWidth="1" style="35" min="23" max="23"/>
-    <col width="0.1640625" customWidth="1" style="35" min="24" max="24"/>
-    <col width="3.33203125" customWidth="1" style="35" min="25" max="25"/>
-    <col width="2.1640625" customWidth="1" style="35" min="26" max="26"/>
-    <col width="1.33203125" customWidth="1" style="35" min="27" max="27"/>
-    <col width="2.1640625" customWidth="1" style="35" min="28" max="28"/>
-    <col width="1.33203125" customWidth="1" style="35" min="29" max="29"/>
-    <col width="4" customWidth="1" style="35" min="30" max="30"/>
-    <col width="1.83203125" customWidth="1" style="35" min="31" max="32"/>
-    <col width="3.5" customWidth="1" style="35" min="33" max="35"/>
-    <col width="2.1640625" customWidth="1" style="35" min="36" max="36"/>
-    <col width="0.33203125" customWidth="1" style="35" min="37" max="37"/>
-    <col width="1" customWidth="1" style="35" min="38" max="38"/>
-    <col width="3.5" customWidth="1" style="35" min="39" max="42"/>
-    <col width="1.33203125" customWidth="1" style="35" min="43" max="43"/>
-    <col width="0.6640625" customWidth="1" style="35" min="44" max="44"/>
-    <col width="2.1640625" customWidth="1" style="35" min="45" max="45"/>
+    <col width="1.1640625" customWidth="1" style="4" min="1" max="1"/>
+    <col width="3.5" customWidth="1" style="4" min="2" max="2"/>
+    <col width="1.83203125" customWidth="1" style="4" min="3" max="3"/>
+    <col width="1.6640625" customWidth="1" style="4" min="4" max="4"/>
+    <col width="3.5" customWidth="1" style="4" min="5" max="5"/>
+    <col width="4.33203125" customWidth="1" style="4" min="6" max="6"/>
+    <col width="2.5" customWidth="1" style="4" min="7" max="7"/>
+    <col width="0.5" customWidth="1" style="4" min="8" max="8"/>
+    <col width="3" customWidth="1" style="4" min="9" max="9"/>
+    <col width="3.5" customWidth="1" style="4" min="10" max="16"/>
+    <col width="2.83203125" customWidth="1" style="4" min="17" max="17"/>
+    <col width="1.33203125" customWidth="1" style="4" min="18" max="19"/>
+    <col width="2.83203125" customWidth="1" style="4" min="20" max="21"/>
+    <col width="2.1640625" customWidth="1" style="4" min="22" max="22"/>
+    <col width="1.33203125" customWidth="1" style="4" min="23" max="23"/>
+    <col width="0.1640625" customWidth="1" style="4" min="24" max="24"/>
+    <col width="3.33203125" customWidth="1" style="4" min="25" max="25"/>
+    <col width="2.1640625" customWidth="1" style="4" min="26" max="26"/>
+    <col width="1.33203125" customWidth="1" style="4" min="27" max="27"/>
+    <col width="2.1640625" customWidth="1" style="4" min="28" max="28"/>
+    <col width="1.33203125" customWidth="1" style="4" min="29" max="29"/>
+    <col width="4" customWidth="1" style="4" min="30" max="30"/>
+    <col width="1.83203125" customWidth="1" style="4" min="31" max="32"/>
+    <col width="3.5" customWidth="1" style="4" min="33" max="35"/>
+    <col width="2.1640625" customWidth="1" style="4" min="36" max="36"/>
+    <col width="0.33203125" customWidth="1" style="4" min="37" max="37"/>
+    <col width="1" customWidth="1" style="4" min="38" max="38"/>
+    <col width="3.5" customWidth="1" style="4" min="39" max="42"/>
+    <col width="1.33203125" customWidth="1" style="4" min="43" max="43"/>
+    <col width="0.6640625" customWidth="1" style="4" min="44" max="44"/>
+    <col width="2.1640625" customWidth="1" style="4" min="45" max="45"/>
   </cols>
   <sheetData>
-    <row r="1" ht="11.1" customHeight="1"/>
-    <row r="2" ht="12.95" customHeight="1">
-      <c r="B2" s="44" t="inlineStr">
+    <row r="1" ht="11.1" customHeight="1" s="12"/>
+    <row r="2" ht="12.95" customHeight="1" s="12">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>ОТДЕЛЕНИЕ "БАНК ТАТАРСТАН" N8610 ПАО СБЕРБАНК</t>
         </is>
       </c>
-      <c r="C2" s="45" t="n"/>
-      <c r="D2" s="45" t="n"/>
-      <c r="E2" s="45" t="n"/>
-      <c r="F2" s="45" t="n"/>
-      <c r="G2" s="45" t="n"/>
-      <c r="H2" s="45" t="n"/>
-      <c r="I2" s="45" t="n"/>
-      <c r="J2" s="45" t="n"/>
-      <c r="K2" s="45" t="n"/>
-      <c r="L2" s="45" t="n"/>
-      <c r="M2" s="45" t="n"/>
-      <c r="N2" s="45" t="n"/>
-      <c r="O2" s="45" t="n"/>
-      <c r="P2" s="45" t="n"/>
-      <c r="Q2" s="45" t="n"/>
-      <c r="R2" s="45" t="n"/>
-      <c r="S2" s="45" t="n"/>
-      <c r="T2" s="45" t="n"/>
-      <c r="U2" s="45" t="n"/>
-      <c r="V2" s="45" t="n"/>
-      <c r="W2" s="46" t="n"/>
-      <c r="X2" s="31" t="inlineStr">
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="46" t="n"/>
+      <c r="E2" s="46" t="n"/>
+      <c r="F2" s="46" t="n"/>
+      <c r="G2" s="46" t="n"/>
+      <c r="H2" s="46" t="n"/>
+      <c r="I2" s="46" t="n"/>
+      <c r="J2" s="46" t="n"/>
+      <c r="K2" s="46" t="n"/>
+      <c r="L2" s="46" t="n"/>
+      <c r="M2" s="46" t="n"/>
+      <c r="N2" s="46" t="n"/>
+      <c r="O2" s="46" t="n"/>
+      <c r="P2" s="46" t="n"/>
+      <c r="Q2" s="46" t="n"/>
+      <c r="R2" s="46" t="n"/>
+      <c r="S2" s="46" t="n"/>
+      <c r="T2" s="46" t="n"/>
+      <c r="U2" s="46" t="n"/>
+      <c r="V2" s="46" t="n"/>
+      <c r="W2" s="47" t="n"/>
+      <c r="X2" s="19" t="inlineStr">
         <is>
           <t>БИК</t>
         </is>
       </c>
-      <c r="Y2" s="47" t="n"/>
-      <c r="Z2" s="47" t="n"/>
-      <c r="AA2" s="47" t="n"/>
-      <c r="AB2" s="47" t="n"/>
-      <c r="AC2" s="48" t="n"/>
-      <c r="AD2" s="32" t="inlineStr">
+      <c r="Y2" s="48" t="n"/>
+      <c r="Z2" s="48" t="n"/>
+      <c r="AA2" s="48" t="n"/>
+      <c r="AB2" s="48" t="n"/>
+      <c r="AC2" s="49" t="n"/>
+      <c r="AD2" s="20" t="inlineStr">
         <is>
           <t>049205603</t>
         </is>
       </c>
-      <c r="AE2" s="45" t="n"/>
-      <c r="AF2" s="45" t="n"/>
-      <c r="AG2" s="45" t="n"/>
-      <c r="AH2" s="45" t="n"/>
-      <c r="AI2" s="45" t="n"/>
-      <c r="AJ2" s="45" t="n"/>
-      <c r="AK2" s="45" t="n"/>
-      <c r="AL2" s="45" t="n"/>
-      <c r="AM2" s="45" t="n"/>
-      <c r="AN2" s="45" t="n"/>
-      <c r="AO2" s="45" t="n"/>
-      <c r="AP2" s="45" t="n"/>
-      <c r="AQ2" s="45" t="n"/>
-      <c r="AR2" s="46" t="n"/>
-    </row>
-    <row r="3" ht="11.1" customHeight="1">
-      <c r="B3" s="49" t="n"/>
-      <c r="W3" s="50" t="n"/>
-      <c r="X3" s="51" t="inlineStr">
+      <c r="AE2" s="46" t="n"/>
+      <c r="AF2" s="46" t="n"/>
+      <c r="AG2" s="46" t="n"/>
+      <c r="AH2" s="46" t="n"/>
+      <c r="AI2" s="46" t="n"/>
+      <c r="AJ2" s="46" t="n"/>
+      <c r="AK2" s="46" t="n"/>
+      <c r="AL2" s="46" t="n"/>
+      <c r="AM2" s="46" t="n"/>
+      <c r="AN2" s="46" t="n"/>
+      <c r="AO2" s="46" t="n"/>
+      <c r="AP2" s="46" t="n"/>
+      <c r="AQ2" s="46" t="n"/>
+      <c r="AR2" s="47" t="n"/>
+    </row>
+    <row r="3" ht="11.1" customHeight="1" s="12">
+      <c r="B3" s="50" t="n"/>
+      <c r="W3" s="51" t="n"/>
+      <c r="X3" s="52" t="inlineStr">
         <is>
           <t>Сч. №</t>
         </is>
       </c>
-      <c r="Y3" s="45" t="n"/>
-      <c r="Z3" s="45" t="n"/>
-      <c r="AA3" s="45" t="n"/>
-      <c r="AB3" s="45" t="n"/>
-      <c r="AC3" s="46" t="n"/>
-      <c r="AD3" s="52" t="inlineStr">
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="47" t="n"/>
+      <c r="AD3" s="53" t="inlineStr">
         <is>
           <t>40502810362210100004</t>
         </is>
       </c>
-      <c r="AR3" s="50" t="n"/>
-    </row>
-    <row r="4" ht="11.1" customHeight="1">
-      <c r="B4" s="34" t="inlineStr">
+      <c r="AR3" s="51" t="n"/>
+    </row>
+    <row r="4" ht="11.1" customHeight="1" s="12">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Банк получателя</t>
         </is>
       </c>
-      <c r="C4" s="53" t="n"/>
-      <c r="D4" s="53" t="n"/>
-      <c r="E4" s="53" t="n"/>
-      <c r="F4" s="53" t="n"/>
-      <c r="G4" s="53" t="n"/>
-      <c r="H4" s="53" t="n"/>
-      <c r="I4" s="53" t="n"/>
-      <c r="J4" s="53" t="n"/>
-      <c r="K4" s="53" t="n"/>
-      <c r="L4" s="53" t="n"/>
-      <c r="M4" s="53" t="n"/>
-      <c r="N4" s="53" t="n"/>
-      <c r="O4" s="53" t="n"/>
-      <c r="P4" s="53" t="n"/>
-      <c r="Q4" s="53" t="n"/>
-      <c r="R4" s="53" t="n"/>
-      <c r="S4" s="53" t="n"/>
-      <c r="T4" s="53" t="n"/>
-      <c r="U4" s="53" t="n"/>
-      <c r="V4" s="53" t="n"/>
-      <c r="W4" s="54" t="n"/>
-      <c r="X4" s="55" t="n"/>
-      <c r="Y4" s="53" t="n"/>
-      <c r="Z4" s="53" t="n"/>
-      <c r="AA4" s="53" t="n"/>
-      <c r="AB4" s="53" t="n"/>
-      <c r="AC4" s="54" t="n"/>
-      <c r="AD4" s="55" t="n"/>
-      <c r="AE4" s="53" t="n"/>
-      <c r="AF4" s="53" t="n"/>
-      <c r="AG4" s="53" t="n"/>
-      <c r="AH4" s="53" t="n"/>
-      <c r="AI4" s="53" t="n"/>
-      <c r="AJ4" s="53" t="n"/>
-      <c r="AK4" s="53" t="n"/>
-      <c r="AL4" s="53" t="n"/>
-      <c r="AM4" s="53" t="n"/>
-      <c r="AN4" s="53" t="n"/>
-      <c r="AO4" s="53" t="n"/>
-      <c r="AP4" s="53" t="n"/>
-      <c r="AQ4" s="53" t="n"/>
-      <c r="AR4" s="54" t="n"/>
-    </row>
-    <row r="5" ht="12.95" customHeight="1">
-      <c r="B5" s="27" t="inlineStr">
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="54" t="n"/>
+      <c r="L4" s="54" t="n"/>
+      <c r="M4" s="54" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="54" t="n"/>
+      <c r="P4" s="54" t="n"/>
+      <c r="Q4" s="54" t="n"/>
+      <c r="R4" s="54" t="n"/>
+      <c r="S4" s="54" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="55" t="n"/>
+      <c r="X4" s="56" t="n"/>
+      <c r="Y4" s="54" t="n"/>
+      <c r="Z4" s="54" t="n"/>
+      <c r="AA4" s="54" t="n"/>
+      <c r="AB4" s="54" t="n"/>
+      <c r="AC4" s="55" t="n"/>
+      <c r="AD4" s="56" t="n"/>
+      <c r="AE4" s="54" t="n"/>
+      <c r="AF4" s="54" t="n"/>
+      <c r="AG4" s="54" t="n"/>
+      <c r="AH4" s="54" t="n"/>
+      <c r="AI4" s="54" t="n"/>
+      <c r="AJ4" s="54" t="n"/>
+      <c r="AK4" s="54" t="n"/>
+      <c r="AL4" s="54" t="n"/>
+      <c r="AM4" s="54" t="n"/>
+      <c r="AN4" s="54" t="n"/>
+      <c r="AO4" s="54" t="n"/>
+      <c r="AP4" s="54" t="n"/>
+      <c r="AQ4" s="54" t="n"/>
+      <c r="AR4" s="55" t="n"/>
+    </row>
+    <row r="5" ht="12.95" customHeight="1" s="12">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>ИНН</t>
         </is>
       </c>
-      <c r="C5" s="45" t="n"/>
-      <c r="D5" s="45" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="45" t="n"/>
-      <c r="G5" s="45" t="n"/>
-      <c r="H5" s="45" t="n"/>
-      <c r="I5" s="45" t="n"/>
-      <c r="J5" s="45" t="n"/>
-      <c r="K5" s="45" t="n"/>
-      <c r="L5" s="46" t="n"/>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="46" t="n"/>
+      <c r="L5" s="47" t="n"/>
+      <c r="M5" s="34" t="inlineStr">
         <is>
           <t>КПП</t>
         </is>
       </c>
-      <c r="N5" s="45" t="n"/>
-      <c r="O5" s="28" t="n"/>
-      <c r="P5" s="45" t="n"/>
-      <c r="Q5" s="45" t="n"/>
-      <c r="R5" s="45" t="n"/>
-      <c r="S5" s="45" t="n"/>
-      <c r="T5" s="45" t="n"/>
-      <c r="U5" s="45" t="n"/>
-      <c r="V5" s="45" t="n"/>
-      <c r="W5" s="46" t="n"/>
-      <c r="X5" s="51" t="inlineStr">
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="35" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="47" t="n"/>
+      <c r="X5" s="52" t="inlineStr">
         <is>
           <t>Сч. №</t>
         </is>
       </c>
-      <c r="Y5" s="45" t="n"/>
-      <c r="Z5" s="45" t="n"/>
-      <c r="AA5" s="45" t="n"/>
-      <c r="AB5" s="45" t="n"/>
-      <c r="AC5" s="46" t="n"/>
-      <c r="AD5" s="51" t="inlineStr">
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="47" t="n"/>
+      <c r="AD5" s="52" t="inlineStr">
         <is>
           <t>30101810600000000603</t>
         </is>
       </c>
-      <c r="AE5" s="45" t="n"/>
-      <c r="AF5" s="45" t="n"/>
-      <c r="AG5" s="45" t="n"/>
-      <c r="AH5" s="45" t="n"/>
-      <c r="AI5" s="45" t="n"/>
-      <c r="AJ5" s="45" t="n"/>
-      <c r="AK5" s="45" t="n"/>
-      <c r="AL5" s="45" t="n"/>
-      <c r="AM5" s="45" t="n"/>
-      <c r="AN5" s="45" t="n"/>
-      <c r="AO5" s="45" t="n"/>
-      <c r="AP5" s="45" t="n"/>
-      <c r="AQ5" s="45" t="n"/>
-      <c r="AR5" s="46" t="n"/>
-    </row>
-    <row r="6" ht="11.1" customHeight="1">
-      <c r="B6" s="22" t="inlineStr">
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="46" t="n"/>
+      <c r="AQ5" s="46" t="n"/>
+      <c r="AR5" s="47" t="n"/>
+    </row>
+    <row r="6" ht="11.1" customHeight="1" s="12">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Филиал ФГУП "Охрана" Росгвардии по Республике Татарстан</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
-      <c r="G6" s="45" t="n"/>
-      <c r="H6" s="45" t="n"/>
-      <c r="I6" s="45" t="n"/>
-      <c r="J6" s="45" t="n"/>
-      <c r="K6" s="45" t="n"/>
-      <c r="L6" s="45" t="n"/>
-      <c r="M6" s="45" t="n"/>
-      <c r="N6" s="45" t="n"/>
-      <c r="O6" s="45" t="n"/>
-      <c r="P6" s="45" t="n"/>
-      <c r="Q6" s="45" t="n"/>
-      <c r="R6" s="45" t="n"/>
-      <c r="S6" s="45" t="n"/>
-      <c r="T6" s="45" t="n"/>
-      <c r="U6" s="45" t="n"/>
-      <c r="V6" s="45" t="n"/>
-      <c r="W6" s="45" t="n"/>
-      <c r="X6" s="49" t="n"/>
-      <c r="AC6" s="50" t="n"/>
-      <c r="AD6" s="49" t="n"/>
-      <c r="AR6" s="50" t="n"/>
-    </row>
-    <row r="7" ht="11.1" customHeight="1">
-      <c r="B7" s="49" t="n"/>
-      <c r="X7" s="49" t="n"/>
-      <c r="AC7" s="50" t="n"/>
-      <c r="AD7" s="49" t="n"/>
-      <c r="AR7" s="50" t="n"/>
-    </row>
-    <row r="8" ht="11.1" customHeight="1">
-      <c r="B8" s="24" t="inlineStr">
+      <c r="C6" s="46" t="n"/>
+      <c r="D6" s="46" t="n"/>
+      <c r="E6" s="46" t="n"/>
+      <c r="F6" s="46" t="n"/>
+      <c r="G6" s="46" t="n"/>
+      <c r="H6" s="46" t="n"/>
+      <c r="I6" s="46" t="n"/>
+      <c r="J6" s="46" t="n"/>
+      <c r="K6" s="46" t="n"/>
+      <c r="L6" s="46" t="n"/>
+      <c r="M6" s="46" t="n"/>
+      <c r="N6" s="46" t="n"/>
+      <c r="O6" s="46" t="n"/>
+      <c r="P6" s="46" t="n"/>
+      <c r="Q6" s="46" t="n"/>
+      <c r="R6" s="46" t="n"/>
+      <c r="S6" s="46" t="n"/>
+      <c r="T6" s="46" t="n"/>
+      <c r="U6" s="46" t="n"/>
+      <c r="V6" s="46" t="n"/>
+      <c r="W6" s="46" t="n"/>
+      <c r="X6" s="50" t="n"/>
+      <c r="AC6" s="51" t="n"/>
+      <c r="AD6" s="50" t="n"/>
+      <c r="AR6" s="51" t="n"/>
+    </row>
+    <row r="7" ht="11.1" customHeight="1" s="12">
+      <c r="B7" s="50" t="n"/>
+      <c r="X7" s="50" t="n"/>
+      <c r="AC7" s="51" t="n"/>
+      <c r="AD7" s="50" t="n"/>
+      <c r="AR7" s="51" t="n"/>
+    </row>
+    <row r="8" ht="11.1" customHeight="1" s="12">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
       </c>
-      <c r="C8" s="53" t="n"/>
-      <c r="D8" s="53" t="n"/>
-      <c r="E8" s="53" t="n"/>
-      <c r="F8" s="53" t="n"/>
-      <c r="G8" s="53" t="n"/>
-      <c r="H8" s="53" t="n"/>
-      <c r="I8" s="53" t="n"/>
-      <c r="J8" s="53" t="n"/>
-      <c r="K8" s="53" t="n"/>
-      <c r="L8" s="53" t="n"/>
-      <c r="M8" s="53" t="n"/>
-      <c r="N8" s="53" t="n"/>
-      <c r="O8" s="53" t="n"/>
-      <c r="P8" s="53" t="n"/>
-      <c r="Q8" s="53" t="n"/>
-      <c r="R8" s="53" t="n"/>
-      <c r="S8" s="53" t="n"/>
-      <c r="T8" s="53" t="n"/>
-      <c r="U8" s="53" t="n"/>
-      <c r="V8" s="53" t="n"/>
-      <c r="W8" s="53" t="n"/>
-      <c r="X8" s="55" t="n"/>
-      <c r="Y8" s="53" t="n"/>
-      <c r="Z8" s="53" t="n"/>
-      <c r="AA8" s="53" t="n"/>
-      <c r="AB8" s="53" t="n"/>
-      <c r="AC8" s="54" t="n"/>
-      <c r="AD8" s="55" t="n"/>
-      <c r="AE8" s="53" t="n"/>
-      <c r="AF8" s="53" t="n"/>
-      <c r="AG8" s="53" t="n"/>
-      <c r="AH8" s="53" t="n"/>
-      <c r="AI8" s="53" t="n"/>
-      <c r="AJ8" s="53" t="n"/>
-      <c r="AK8" s="53" t="n"/>
-      <c r="AL8" s="53" t="n"/>
-      <c r="AM8" s="53" t="n"/>
-      <c r="AN8" s="53" t="n"/>
-      <c r="AO8" s="53" t="n"/>
-      <c r="AP8" s="53" t="n"/>
-      <c r="AQ8" s="53" t="n"/>
-      <c r="AR8" s="54" t="n"/>
-    </row>
-    <row r="10" ht="11.1" customHeight="1">
-      <c r="B10" s="25" t="inlineStr">
+      <c r="C8" s="54" t="n"/>
+      <c r="D8" s="54" t="n"/>
+      <c r="E8" s="54" t="n"/>
+      <c r="F8" s="54" t="n"/>
+      <c r="G8" s="54" t="n"/>
+      <c r="H8" s="54" t="n"/>
+      <c r="I8" s="54" t="n"/>
+      <c r="J8" s="54" t="n"/>
+      <c r="K8" s="54" t="n"/>
+      <c r="L8" s="54" t="n"/>
+      <c r="M8" s="54" t="n"/>
+      <c r="N8" s="54" t="n"/>
+      <c r="O8" s="54" t="n"/>
+      <c r="P8" s="54" t="n"/>
+      <c r="Q8" s="54" t="n"/>
+      <c r="R8" s="54" t="n"/>
+      <c r="S8" s="54" t="n"/>
+      <c r="T8" s="54" t="n"/>
+      <c r="U8" s="54" t="n"/>
+      <c r="V8" s="54" t="n"/>
+      <c r="W8" s="54" t="n"/>
+      <c r="X8" s="56" t="n"/>
+      <c r="Y8" s="54" t="n"/>
+      <c r="Z8" s="54" t="n"/>
+      <c r="AA8" s="54" t="n"/>
+      <c r="AB8" s="54" t="n"/>
+      <c r="AC8" s="55" t="n"/>
+      <c r="AD8" s="56" t="n"/>
+      <c r="AE8" s="54" t="n"/>
+      <c r="AF8" s="54" t="n"/>
+      <c r="AG8" s="54" t="n"/>
+      <c r="AH8" s="54" t="n"/>
+      <c r="AI8" s="54" t="n"/>
+      <c r="AJ8" s="54" t="n"/>
+      <c r="AK8" s="54" t="n"/>
+      <c r="AL8" s="54" t="n"/>
+      <c r="AM8" s="54" t="n"/>
+      <c r="AN8" s="54" t="n"/>
+      <c r="AO8" s="54" t="n"/>
+      <c r="AP8" s="54" t="n"/>
+      <c r="AQ8" s="54" t="n"/>
+      <c r="AR8" s="55" t="n"/>
+    </row>
+    <row r="10" ht="11.1" customHeight="1" s="12">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>Счет на оплату №16-187923 от 15.12.2020  г.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="11.1" customHeight="1"/>
-    <row r="12" ht="6.95" customFormat="1" customHeight="1" s="35">
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="56" t="n"/>
-      <c r="D12" s="56" t="n"/>
-      <c r="E12" s="56" t="n"/>
-      <c r="F12" s="56" t="n"/>
-      <c r="G12" s="56" t="n"/>
-      <c r="H12" s="56" t="n"/>
-      <c r="I12" s="56" t="n"/>
-      <c r="J12" s="56" t="n"/>
-      <c r="K12" s="56" t="n"/>
-      <c r="L12" s="56" t="n"/>
-      <c r="M12" s="56" t="n"/>
-      <c r="N12" s="56" t="n"/>
-      <c r="O12" s="56" t="n"/>
-      <c r="P12" s="56" t="n"/>
-      <c r="Q12" s="56" t="n"/>
-      <c r="R12" s="56" t="n"/>
-      <c r="S12" s="56" t="n"/>
-      <c r="T12" s="56" t="n"/>
-      <c r="U12" s="56" t="n"/>
-      <c r="V12" s="56" t="n"/>
-      <c r="W12" s="56" t="n"/>
-      <c r="X12" s="56" t="n"/>
-      <c r="Y12" s="56" t="n"/>
-      <c r="Z12" s="56" t="n"/>
-      <c r="AA12" s="56" t="n"/>
-      <c r="AB12" s="56" t="n"/>
-      <c r="AC12" s="56" t="n"/>
-      <c r="AD12" s="56" t="n"/>
-      <c r="AE12" s="56" t="n"/>
-      <c r="AF12" s="56" t="n"/>
-      <c r="AG12" s="56" t="n"/>
-      <c r="AH12" s="56" t="n"/>
-      <c r="AI12" s="56" t="n"/>
-      <c r="AJ12" s="56" t="n"/>
-      <c r="AK12" s="56" t="n"/>
-      <c r="AL12" s="56" t="n"/>
-      <c r="AM12" s="56" t="n"/>
-      <c r="AN12" s="56" t="n"/>
-      <c r="AO12" s="56" t="n"/>
-      <c r="AP12" s="56" t="n"/>
-      <c r="AQ12" s="56" t="n"/>
-      <c r="AR12" s="56" t="n"/>
-    </row>
-    <row r="13" ht="6.95" customFormat="1" customHeight="1" s="35"/>
-    <row r="14" ht="14.1" customHeight="1">
-      <c r="B14" s="14" t="inlineStr">
+    <row r="11" ht="11.1" customHeight="1" s="12"/>
+    <row r="12" ht="6.95" customFormat="1" customHeight="1" s="4">
+      <c r="B12" s="33" t="n"/>
+      <c r="C12" s="57" t="n"/>
+      <c r="D12" s="57" t="n"/>
+      <c r="E12" s="57" t="n"/>
+      <c r="F12" s="57" t="n"/>
+      <c r="G12" s="57" t="n"/>
+      <c r="H12" s="57" t="n"/>
+      <c r="I12" s="57" t="n"/>
+      <c r="J12" s="57" t="n"/>
+      <c r="K12" s="57" t="n"/>
+      <c r="L12" s="57" t="n"/>
+      <c r="M12" s="57" t="n"/>
+      <c r="N12" s="57" t="n"/>
+      <c r="O12" s="57" t="n"/>
+      <c r="P12" s="57" t="n"/>
+      <c r="Q12" s="57" t="n"/>
+      <c r="R12" s="57" t="n"/>
+      <c r="S12" s="57" t="n"/>
+      <c r="T12" s="57" t="n"/>
+      <c r="U12" s="57" t="n"/>
+      <c r="V12" s="57" t="n"/>
+      <c r="W12" s="57" t="n"/>
+      <c r="X12" s="57" t="n"/>
+      <c r="Y12" s="57" t="n"/>
+      <c r="Z12" s="57" t="n"/>
+      <c r="AA12" s="57" t="n"/>
+      <c r="AB12" s="57" t="n"/>
+      <c r="AC12" s="57" t="n"/>
+      <c r="AD12" s="57" t="n"/>
+      <c r="AE12" s="57" t="n"/>
+      <c r="AF12" s="57" t="n"/>
+      <c r="AG12" s="57" t="n"/>
+      <c r="AH12" s="57" t="n"/>
+      <c r="AI12" s="57" t="n"/>
+      <c r="AJ12" s="57" t="n"/>
+      <c r="AK12" s="57" t="n"/>
+      <c r="AL12" s="57" t="n"/>
+      <c r="AM12" s="57" t="n"/>
+      <c r="AN12" s="57" t="n"/>
+      <c r="AO12" s="57" t="n"/>
+      <c r="AP12" s="57" t="n"/>
+      <c r="AQ12" s="57" t="n"/>
+      <c r="AR12" s="57" t="n"/>
+    </row>
+    <row r="13" ht="6.95" customFormat="1" customHeight="1" s="4"/>
+    <row r="14" ht="14.1" customHeight="1" s="12">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Поставщик
 (Исполнитель):</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="36" t="inlineStr">
         <is>
           <t>Филиал ФГУП "Охрана" Росгвардии по Республике Татарстан,127473, Москва г, Делегатская ул, дом 5, строение 1</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="11.1" customFormat="1" customHeight="1" s="35"/>
-    <row r="16" ht="6.95" customFormat="1" customHeight="1" s="35"/>
-    <row r="17" ht="14.1" customHeight="1">
-      <c r="B17" s="14" t="inlineStr">
+    <row r="15" ht="11.1" customFormat="1" customHeight="1" s="4"/>
+    <row r="16" ht="6.95" customFormat="1" customHeight="1" s="4"/>
+    <row r="17" ht="14.1" customHeight="1" s="12">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Покупатель
 (Заказчик):</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="36" t="inlineStr">
         <is>
           <t>ООО "ЭСПЕРАНС",119049, РФ, г.Москва, 1-й Добрынинский пер.,д.19, стр.6, пом.III, комната 1, этаж 1</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="11.1" customFormat="1" customHeight="1" s="35"/>
-    <row r="19" ht="6.95" customFormat="1" customHeight="1" s="35"/>
-    <row r="20" ht="12.95" customHeight="1">
-      <c r="B20" s="15" t="inlineStr">
+    <row r="18" ht="11.1" customFormat="1" customHeight="1" s="4"/>
+    <row r="19" ht="6.95" customFormat="1" customHeight="1" s="4"/>
+    <row r="20" ht="12.95" customHeight="1" s="12">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Основание:</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="36" t="inlineStr">
         <is>
           <t>№113/4 от 01.09.2013 (новый перечень от 01.01.2019)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="6.95" customFormat="1" customHeight="1" s="35"/>
-    <row r="22" ht="12.95" customHeight="1">
-      <c r="B22" s="12" t="inlineStr">
+    <row r="21" ht="6.95" customFormat="1" customHeight="1" s="4"/>
+    <row r="22" ht="12.95" customHeight="1" s="12">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="C22" s="57" t="n"/>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="C22" s="58" t="n"/>
+      <c r="D22" s="44" t="inlineStr">
         <is>
           <t>Товары (работы, услуги)</t>
         </is>
       </c>
-      <c r="E22" s="57" t="n"/>
-      <c r="F22" s="57" t="n"/>
-      <c r="G22" s="57" t="n"/>
-      <c r="H22" s="57" t="n"/>
-      <c r="I22" s="57" t="n"/>
-      <c r="J22" s="57" t="n"/>
-      <c r="K22" s="57" t="n"/>
-      <c r="L22" s="57" t="n"/>
-      <c r="M22" s="57" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="O22" s="57" t="n"/>
-      <c r="P22" s="57" t="n"/>
-      <c r="Q22" s="57" t="n"/>
-      <c r="R22" s="57" t="n"/>
-      <c r="S22" s="57" t="n"/>
-      <c r="T22" s="57" t="n"/>
-      <c r="U22" s="57" t="n"/>
-      <c r="V22" s="57" t="n"/>
-      <c r="W22" s="57" t="n"/>
-      <c r="X22" s="57" t="n"/>
-      <c r="Y22" s="13" t="inlineStr">
+      <c r="E22" s="58" t="n"/>
+      <c r="F22" s="58" t="n"/>
+      <c r="G22" s="58" t="n"/>
+      <c r="H22" s="58" t="n"/>
+      <c r="I22" s="58" t="n"/>
+      <c r="J22" s="58" t="n"/>
+      <c r="K22" s="58" t="n"/>
+      <c r="L22" s="58" t="n"/>
+      <c r="M22" s="58" t="n"/>
+      <c r="N22" s="58" t="n"/>
+      <c r="O22" s="58" t="n"/>
+      <c r="P22" s="58" t="n"/>
+      <c r="Q22" s="58" t="n"/>
+      <c r="R22" s="58" t="n"/>
+      <c r="S22" s="58" t="n"/>
+      <c r="T22" s="58" t="n"/>
+      <c r="U22" s="58" t="n"/>
+      <c r="V22" s="58" t="n"/>
+      <c r="W22" s="58" t="n"/>
+      <c r="X22" s="58" t="n"/>
+      <c r="Y22" s="44" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="Z22" s="57" t="n"/>
-      <c r="AA22" s="57" t="n"/>
-      <c r="AB22" s="57" t="n"/>
-      <c r="AC22" s="13" t="inlineStr">
+      <c r="Z22" s="58" t="n"/>
+      <c r="AA22" s="58" t="n"/>
+      <c r="AB22" s="58" t="n"/>
+      <c r="AC22" s="44" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="AD22" s="57" t="n"/>
-      <c r="AE22" s="57" t="n"/>
-      <c r="AF22" s="13" t="inlineStr">
+      <c r="AD22" s="58" t="n"/>
+      <c r="AE22" s="58" t="n"/>
+      <c r="AF22" s="44" t="inlineStr">
         <is>
           <t>Цена</t>
         </is>
       </c>
-      <c r="AG22" s="57" t="n"/>
-      <c r="AH22" s="57" t="n"/>
-      <c r="AI22" s="57" t="n"/>
-      <c r="AJ22" s="57" t="n"/>
-      <c r="AK22" s="11" t="inlineStr">
+      <c r="AG22" s="58" t="n"/>
+      <c r="AH22" s="58" t="n"/>
+      <c r="AI22" s="58" t="n"/>
+      <c r="AJ22" s="58" t="n"/>
+      <c r="AK22" s="38" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="AL22" s="57" t="n"/>
-      <c r="AM22" s="57" t="n"/>
-      <c r="AN22" s="57" t="n"/>
-      <c r="AO22" s="57" t="n"/>
-      <c r="AP22" s="57" t="n"/>
-      <c r="AQ22" s="58" t="n"/>
-    </row>
-    <row r="23" ht="50" customHeight="1">
-      <c r="B23" s="59" t="n">
+      <c r="AL22" s="58" t="n"/>
+      <c r="AM22" s="58" t="n"/>
+      <c r="AN22" s="58" t="n"/>
+      <c r="AO22" s="58" t="n"/>
+      <c r="AP22" s="58" t="n"/>
+      <c r="AQ22" s="59" t="n"/>
+    </row>
+    <row r="23" ht="50" customHeight="1" s="12">
+      <c r="B23" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="60" t="n"/>
-      <c r="D23" s="60" t="inlineStr">
+      <c r="C23" s="61" t="n"/>
+      <c r="D23" s="61" t="inlineStr">
         <is>
           <t>Оказание услуг по техническому обслуживанию технических средств охраны</t>
         </is>
       </c>
-      <c r="E23" s="60" t="n"/>
-      <c r="F23" s="60" t="n"/>
-      <c r="G23" s="60" t="n"/>
-      <c r="H23" s="60" t="n"/>
-      <c r="I23" s="60" t="n"/>
-      <c r="J23" s="60" t="n"/>
-      <c r="K23" s="60" t="n"/>
-      <c r="L23" s="60" t="n"/>
-      <c r="M23" s="60" t="n"/>
-      <c r="N23" s="60" t="n"/>
-      <c r="O23" s="60" t="n"/>
-      <c r="P23" s="60" t="n"/>
-      <c r="Q23" s="60" t="n"/>
-      <c r="R23" s="60" t="n"/>
-      <c r="S23" s="60" t="n"/>
-      <c r="T23" s="60" t="n"/>
-      <c r="U23" s="60" t="n"/>
-      <c r="V23" s="60" t="n"/>
-      <c r="W23" s="60" t="n"/>
-      <c r="X23" s="60" t="n"/>
-      <c r="Y23" s="60" t="n"/>
-      <c r="Z23" s="60" t="n"/>
-      <c r="AA23" s="60" t="n"/>
-      <c r="AB23" s="60" t="n"/>
-      <c r="AC23" s="60" t="n"/>
-      <c r="AD23" s="60" t="n"/>
-      <c r="AE23" s="60" t="n"/>
-      <c r="AF23" s="61" t="n"/>
-      <c r="AG23" s="60" t="n"/>
-      <c r="AH23" s="60" t="n"/>
-      <c r="AI23" s="60" t="n"/>
-      <c r="AJ23" s="60" t="n"/>
-      <c r="AK23" s="61" t="n"/>
-      <c r="AL23" s="60" t="n"/>
-      <c r="AM23" s="60" t="n"/>
-      <c r="AN23" s="60" t="n"/>
-      <c r="AO23" s="60" t="n"/>
-      <c r="AP23" s="60" t="n"/>
-      <c r="AQ23" s="62" t="n"/>
-    </row>
-    <row r="24" ht="50" customFormat="1" customHeight="1" s="35">
-      <c r="B24" s="63" t="n">
+      <c r="E23" s="61" t="n"/>
+      <c r="F23" s="61" t="n"/>
+      <c r="G23" s="61" t="n"/>
+      <c r="H23" s="61" t="n"/>
+      <c r="I23" s="61" t="n"/>
+      <c r="J23" s="61" t="n"/>
+      <c r="K23" s="61" t="n"/>
+      <c r="L23" s="61" t="n"/>
+      <c r="M23" s="61" t="n"/>
+      <c r="N23" s="61" t="n"/>
+      <c r="O23" s="61" t="n"/>
+      <c r="P23" s="61" t="n"/>
+      <c r="Q23" s="61" t="n"/>
+      <c r="R23" s="61" t="n"/>
+      <c r="S23" s="61" t="n"/>
+      <c r="T23" s="61" t="n"/>
+      <c r="U23" s="61" t="n"/>
+      <c r="V23" s="61" t="n"/>
+      <c r="W23" s="61" t="n"/>
+      <c r="X23" s="61" t="n"/>
+      <c r="Y23" s="61" t="n"/>
+      <c r="Z23" s="61" t="n"/>
+      <c r="AA23" s="61" t="n"/>
+      <c r="AB23" s="61" t="n"/>
+      <c r="AC23" s="61" t="n"/>
+      <c r="AD23" s="61" t="n"/>
+      <c r="AE23" s="61" t="n"/>
+      <c r="AF23" s="62" t="inlineStr">
+        <is>
+          <t>1812.35</t>
+        </is>
+      </c>
+      <c r="AG23" s="61" t="n"/>
+      <c r="AH23" s="61" t="n"/>
+      <c r="AI23" s="61" t="n"/>
+      <c r="AJ23" s="61" t="n"/>
+      <c r="AK23" s="62" t="inlineStr">
+        <is>
+          <t>1812.35</t>
+        </is>
+      </c>
+      <c r="AL23" s="61" t="n"/>
+      <c r="AM23" s="61" t="n"/>
+      <c r="AN23" s="61" t="n"/>
+      <c r="AO23" s="61" t="n"/>
+      <c r="AP23" s="61" t="n"/>
+      <c r="AQ23" s="63" t="n"/>
+    </row>
+    <row r="24" ht="50" customFormat="1" customHeight="1" s="4">
+      <c r="B24" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="64" t="n"/>
-      <c r="D24" s="64" t="inlineStr">
-        <is>
-          <t>Сосание хуев</t>
-        </is>
-      </c>
-      <c r="E24" s="64" t="n"/>
-      <c r="F24" s="64" t="n"/>
-      <c r="G24" s="64" t="n"/>
-      <c r="H24" s="64" t="n"/>
-      <c r="I24" s="64" t="n"/>
-      <c r="J24" s="64" t="n"/>
-      <c r="K24" s="64" t="n"/>
-      <c r="L24" s="64" t="n"/>
-      <c r="M24" s="64" t="n"/>
-      <c r="N24" s="64" t="n"/>
-      <c r="O24" s="64" t="n"/>
-      <c r="P24" s="64" t="n"/>
-      <c r="Q24" s="64" t="n"/>
-      <c r="R24" s="64" t="n"/>
-      <c r="S24" s="64" t="n"/>
-      <c r="T24" s="64" t="n"/>
-      <c r="U24" s="64" t="n"/>
-      <c r="V24" s="64" t="n"/>
-      <c r="W24" s="64" t="n"/>
-      <c r="X24" s="64" t="n"/>
-      <c r="Y24" s="64" t="n"/>
-      <c r="Z24" s="64" t="n"/>
-      <c r="AA24" s="64" t="n"/>
-      <c r="AB24" s="64" t="n"/>
-      <c r="AC24" s="64" t="n"/>
-      <c r="AD24" s="64" t="n"/>
-      <c r="AE24" s="64" t="n"/>
-      <c r="AF24" s="64" t="n"/>
-      <c r="AG24" s="64" t="n"/>
-      <c r="AH24" s="64" t="n"/>
-      <c r="AI24" s="64" t="n"/>
-      <c r="AJ24" s="64" t="n"/>
-      <c r="AK24" s="64" t="n"/>
-      <c r="AL24" s="64" t="n"/>
-      <c r="AM24" s="64" t="n"/>
-      <c r="AN24" s="64" t="n"/>
-      <c r="AO24" s="64" t="n"/>
-      <c r="AP24" s="64" t="n"/>
-      <c r="AQ24" s="63" t="n"/>
-    </row>
-    <row r="25" ht="12.95" customHeight="1">
-      <c r="AA25" s="3" t="n"/>
-      <c r="AB25" s="3" t="n"/>
-      <c r="AC25" s="3" t="n"/>
-      <c r="AD25" s="3" t="n"/>
-      <c r="AE25" s="3" t="n"/>
-      <c r="AF25" s="3" t="n"/>
-      <c r="AG25" s="3" t="n"/>
-      <c r="AH25" s="3" t="n"/>
-      <c r="AI25" s="3" t="n"/>
-      <c r="AJ25" s="3" t="n"/>
-      <c r="AK25" s="3" t="inlineStr">
+      <c r="C24" s="65" t="n"/>
+      <c r="D24" s="65" t="inlineStr">
+        <is>
+          <t>Покупка ПК</t>
+        </is>
+      </c>
+      <c r="E24" s="65" t="n"/>
+      <c r="F24" s="65" t="n"/>
+      <c r="G24" s="65" t="n"/>
+      <c r="H24" s="65" t="n"/>
+      <c r="I24" s="65" t="n"/>
+      <c r="J24" s="65" t="n"/>
+      <c r="K24" s="65" t="n"/>
+      <c r="L24" s="65" t="n"/>
+      <c r="M24" s="65" t="n"/>
+      <c r="N24" s="65" t="n"/>
+      <c r="O24" s="65" t="n"/>
+      <c r="P24" s="65" t="n"/>
+      <c r="Q24" s="65" t="n"/>
+      <c r="R24" s="65" t="n"/>
+      <c r="S24" s="65" t="n"/>
+      <c r="T24" s="65" t="n"/>
+      <c r="U24" s="65" t="n"/>
+      <c r="V24" s="65" t="n"/>
+      <c r="W24" s="65" t="n"/>
+      <c r="X24" s="65" t="n"/>
+      <c r="Y24" s="65" t="n"/>
+      <c r="Z24" s="65" t="n"/>
+      <c r="AA24" s="65" t="n"/>
+      <c r="AB24" s="65" t="n"/>
+      <c r="AC24" s="65" t="n"/>
+      <c r="AD24" s="65" t="n"/>
+      <c r="AE24" s="65" t="n"/>
+      <c r="AF24" s="65" t="inlineStr">
+        <is>
+          <t>2000.00</t>
+        </is>
+      </c>
+      <c r="AG24" s="65" t="n"/>
+      <c r="AH24" s="65" t="n"/>
+      <c r="AI24" s="65" t="n"/>
+      <c r="AJ24" s="65" t="n"/>
+      <c r="AK24" s="65" t="inlineStr">
+        <is>
+          <t>2000.00</t>
+        </is>
+      </c>
+      <c r="AL24" s="65" t="n"/>
+      <c r="AM24" s="65" t="n"/>
+      <c r="AN24" s="65" t="n"/>
+      <c r="AO24" s="65" t="n"/>
+      <c r="AP24" s="65" t="n"/>
+      <c r="AQ24" s="64" t="n"/>
+    </row>
+    <row r="25" ht="12.95" customHeight="1" s="12">
+      <c r="AA25" s="2" t="n"/>
+      <c r="AB25" s="2" t="n"/>
+      <c r="AC25" s="2" t="n"/>
+      <c r="AD25" s="2" t="n"/>
+      <c r="AE25" s="2" t="n"/>
+      <c r="AF25" s="2" t="n"/>
+      <c r="AG25" s="2" t="n"/>
+      <c r="AH25" s="2" t="n"/>
+      <c r="AI25" s="2" t="n"/>
+      <c r="AJ25" s="2" t="n"/>
+      <c r="AK25" s="2" t="n"/>
+      <c r="AL25" s="37" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="12">
+      <c r="AA26" s="2" t="n"/>
+      <c r="AB26" s="2" t="n"/>
+      <c r="AC26" s="2" t="n"/>
+      <c r="AD26" s="2" t="n"/>
+      <c r="AE26" s="2" t="n"/>
+      <c r="AF26" s="2" t="n"/>
+      <c r="AG26" s="2" t="n"/>
+      <c r="AH26" s="2" t="n"/>
+      <c r="AI26" s="2" t="n"/>
+      <c r="AJ26" s="2" t="n"/>
+      <c r="AK26" s="66" t="inlineStr">
         <is>
           <t>Итого:</t>
         </is>
       </c>
-      <c r="AL25" s="8" t="n"/>
-    </row>
-    <row r="26" ht="12.95" customHeight="1">
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
-      <c r="AC26" s="3" t="n"/>
-      <c r="AD26" s="3" t="n"/>
-      <c r="AE26" s="3" t="n"/>
-      <c r="AF26" s="3" t="n"/>
-      <c r="AG26" s="3" t="n"/>
-      <c r="AH26" s="3" t="n"/>
-      <c r="AI26" s="3" t="n"/>
-      <c r="AJ26" s="3" t="n"/>
-      <c r="AK26" s="3" t="inlineStr">
+      <c r="AL26" s="67" t="inlineStr">
+        <is>
+          <t>1812.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="12">
+      <c r="AA27" s="2" t="n"/>
+      <c r="AB27" s="2" t="n"/>
+      <c r="AC27" s="2" t="n"/>
+      <c r="AD27" s="2" t="n"/>
+      <c r="AE27" s="2" t="n"/>
+      <c r="AF27" s="2" t="n"/>
+      <c r="AG27" s="2" t="n"/>
+      <c r="AH27" s="2" t="n"/>
+      <c r="AI27" s="2" t="n"/>
+      <c r="AJ27" s="2" t="n"/>
+      <c r="AK27" s="66" t="inlineStr">
         <is>
           <t>В том числе НДС:</t>
         </is>
       </c>
-      <c r="AL26" s="8" t="n"/>
-    </row>
-    <row r="27" ht="12.95" customHeight="1">
-      <c r="AA27" s="3" t="n"/>
-      <c r="AB27" s="3" t="n"/>
-      <c r="AC27" s="3" t="n"/>
-      <c r="AD27" s="3" t="n"/>
-      <c r="AE27" s="3" t="n"/>
-      <c r="AF27" s="3" t="n"/>
-      <c r="AG27" s="3" t="n"/>
-      <c r="AH27" s="3" t="n"/>
-      <c r="AI27" s="3" t="n"/>
-      <c r="AJ27" s="3" t="n"/>
-      <c r="AK27" s="3" t="inlineStr">
+      <c r="AL27" s="67" t="inlineStr">
+        <is>
+          <t>302.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="12">
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="n"/>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" s="9" t="n"/>
+      <c r="M28" s="9" t="n"/>
+      <c r="N28" s="9" t="n"/>
+      <c r="O28" s="9" t="n"/>
+      <c r="P28" s="9" t="n"/>
+      <c r="Q28" s="9" t="n"/>
+      <c r="R28" s="9" t="n"/>
+      <c r="S28" s="9" t="n"/>
+      <c r="T28" s="9" t="n"/>
+      <c r="U28" s="9" t="n"/>
+      <c r="V28" s="9" t="n"/>
+      <c r="W28" s="9" t="n"/>
+      <c r="X28" s="9" t="n"/>
+      <c r="Y28" s="9" t="n"/>
+      <c r="Z28" s="9" t="n"/>
+      <c r="AA28" s="9" t="n"/>
+      <c r="AB28" s="9" t="n"/>
+      <c r="AC28" s="9" t="n"/>
+      <c r="AD28" s="9" t="n"/>
+      <c r="AE28" s="9" t="n"/>
+      <c r="AF28" s="9" t="n"/>
+      <c r="AG28" s="9" t="n"/>
+      <c r="AH28" s="9" t="n"/>
+      <c r="AI28" s="9" t="n"/>
+      <c r="AJ28" s="9" t="n"/>
+      <c r="AK28" s="68" t="inlineStr">
         <is>
           <t>Всего к оплате:</t>
         </is>
       </c>
-      <c r="AL27" s="8" t="n"/>
-    </row>
-    <row r="28" ht="12.95" customHeight="1">
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Всего наименований  , на сумму                  руб.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="12.95" customHeight="1">
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Два миллиона пятьсот тысяч рублей 00 копеек</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="6.95" customFormat="1" customHeight="1" s="35"/>
-    <row r="31" ht="12" customFormat="1" customHeight="1" s="35">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="AL28" s="68" t="inlineStr">
+        <is>
+          <t>1812.35</t>
+        </is>
+      </c>
+      <c r="AR28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="13" customHeight="1" s="12">
+      <c r="B29" s="69" t="inlineStr">
+        <is>
+          <t>Всего наименований 2 на сумму 1812.35 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="13" customFormat="1" customHeight="1" s="4">
+      <c r="B30" s="70" t="inlineStr">
+        <is>
+          <t>Одна тысяча восемьсот двенадцать рублей 35 копеек</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="12" customFormat="1" customHeight="1" s="4">
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="O31" s="11" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="11" t="n"/>
+      <c r="R31" s="11" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="11" t="n"/>
+      <c r="U31" s="11" t="n"/>
+      <c r="V31" s="11" t="n"/>
+      <c r="W31" s="11" t="n"/>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="11" t="n"/>
+      <c r="Z31" s="11" t="n"/>
+      <c r="AA31" s="11" t="n"/>
+      <c r="AB31" s="11" t="n"/>
+      <c r="AC31" s="11" t="n"/>
+      <c r="AD31" s="11" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="11" t="n"/>
+      <c r="AG31" s="11" t="n"/>
+      <c r="AH31" s="11" t="n"/>
+      <c r="AI31" s="11" t="n"/>
+      <c r="AJ31" s="11" t="n"/>
+      <c r="AK31" s="11" t="n"/>
+      <c r="AL31" s="11" t="n"/>
+      <c r="AM31" s="11" t="n"/>
+      <c r="AN31" s="11" t="n"/>
+      <c r="AO31" s="11" t="n"/>
+      <c r="AP31" s="11" t="n"/>
+      <c r="AQ31" s="11" t="n"/>
+      <c r="AR31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="13" customFormat="1" customHeight="1" s="4">
+      <c r="B32" s="71" t="inlineStr">
         <is>
           <t>Внимание!</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="12" customFormat="1" customHeight="1" s="35">
-      <c r="B32" s="6" t="inlineStr">
+      <c r="AR32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="13" customFormat="1" customHeight="1" s="4">
+      <c r="B33" s="71" t="inlineStr">
         <is>
           <t>Оплата данного счета означает согласие с условиями поставки товара.</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="12" customFormat="1" customHeight="1" s="35">
-      <c r="B33" s="6" t="inlineStr">
+      <c r="AR33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="13" customFormat="1" customHeight="1" s="4">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="71" t="inlineStr">
         <is>
           <t>Уведомление об оплате обязательно, в противном случае не гарантируется наличие товара на складе.</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="24" customFormat="1" customHeight="1" s="35">
-      <c r="B34" s="6" t="inlineStr">
+      <c r="AR34" s="11" t="n"/>
+      <c r="AS34" s="4" t="n"/>
+      <c r="AT34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26" customFormat="1" customHeight="1" s="4">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="71" t="inlineStr">
         <is>
           <t>Товар отпускается по факту прихода денег на р/с Поставщика, самовывозом, при наличии доверенности и паспорта.</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="6.95" customFormat="1" customHeight="1" s="35">
-      <c r="B35" s="26" t="n"/>
-      <c r="C35" s="26" t="n"/>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="26" t="n"/>
-      <c r="G35" s="26" t="n"/>
-      <c r="H35" s="26" t="n"/>
-      <c r="I35" s="26" t="n"/>
-      <c r="J35" s="26" t="n"/>
-      <c r="K35" s="26" t="n"/>
-      <c r="L35" s="26" t="n"/>
-      <c r="M35" s="26" t="n"/>
-      <c r="N35" s="26" t="n"/>
-      <c r="O35" s="26" t="n"/>
-      <c r="P35" s="26" t="n"/>
-      <c r="Q35" s="26" t="n"/>
-      <c r="R35" s="26" t="n"/>
-      <c r="S35" s="26" t="n"/>
-      <c r="T35" s="26" t="n"/>
-      <c r="U35" s="26" t="n"/>
-      <c r="V35" s="26" t="n"/>
-      <c r="W35" s="26" t="n"/>
-      <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="26" t="n"/>
-      <c r="Z35" s="26" t="n"/>
-      <c r="AA35" s="26" t="n"/>
-      <c r="AB35" s="26" t="n"/>
-      <c r="AC35" s="26" t="n"/>
-      <c r="AD35" s="26" t="n"/>
-      <c r="AE35" s="26" t="n"/>
-      <c r="AF35" s="26" t="n"/>
-      <c r="AG35" s="26" t="n"/>
-      <c r="AH35" s="26" t="n"/>
-      <c r="AI35" s="26" t="n"/>
-      <c r="AJ35" s="26" t="n"/>
-      <c r="AK35" s="26" t="n"/>
-      <c r="AL35" s="26" t="n"/>
-      <c r="AM35" s="26" t="n"/>
-      <c r="AN35" s="26" t="n"/>
-      <c r="AO35" s="26" t="n"/>
-      <c r="AP35" s="26" t="n"/>
-      <c r="AQ35" s="26" t="n"/>
-      <c r="AR35" s="26" t="n"/>
-    </row>
-    <row r="37" ht="12.95" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
+      <c r="AR35" s="4" t="n"/>
+      <c r="AS35" s="4" t="n"/>
+      <c r="AT35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="11.45" customHeight="1" s="12">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="72" t="n"/>
+      <c r="C36" s="72" t="n"/>
+      <c r="D36" s="72" t="n"/>
+      <c r="E36" s="72" t="n"/>
+      <c r="F36" s="72" t="n"/>
+      <c r="G36" s="72" t="n"/>
+      <c r="H36" s="72" t="n"/>
+      <c r="I36" s="72" t="n"/>
+      <c r="J36" s="72" t="n"/>
+      <c r="K36" s="72" t="n"/>
+      <c r="L36" s="72" t="n"/>
+      <c r="M36" s="72" t="n"/>
+      <c r="N36" s="72" t="n"/>
+      <c r="O36" s="72" t="n"/>
+      <c r="P36" s="72" t="n"/>
+      <c r="Q36" s="72" t="n"/>
+      <c r="R36" s="72" t="n"/>
+      <c r="S36" s="72" t="n"/>
+      <c r="T36" s="72" t="n"/>
+      <c r="U36" s="72" t="n"/>
+      <c r="V36" s="72" t="n"/>
+      <c r="W36" s="72" t="n"/>
+      <c r="X36" s="72" t="n"/>
+      <c r="Y36" s="72" t="n"/>
+      <c r="Z36" s="72" t="n"/>
+      <c r="AA36" s="72" t="n"/>
+      <c r="AB36" s="72" t="n"/>
+      <c r="AC36" s="72" t="n"/>
+      <c r="AD36" s="72" t="n"/>
+      <c r="AE36" s="72" t="n"/>
+      <c r="AF36" s="72" t="n"/>
+      <c r="AG36" s="72" t="n"/>
+      <c r="AH36" s="72" t="n"/>
+      <c r="AI36" s="72" t="n"/>
+      <c r="AJ36" s="72" t="n"/>
+      <c r="AK36" s="72" t="n"/>
+      <c r="AL36" s="72" t="n"/>
+      <c r="AM36" s="72" t="n"/>
+      <c r="AN36" s="72" t="n"/>
+      <c r="AO36" s="72" t="n"/>
+      <c r="AP36" s="72" t="n"/>
+      <c r="AQ36" s="72" t="n"/>
+      <c r="AR36" s="4" t="n"/>
+      <c r="AS36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="12.95" customHeight="1" s="12">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="14" t="n"/>
+      <c r="N37" s="14" t="n"/>
+      <c r="O37" s="14" t="n"/>
+      <c r="P37" s="14" t="n"/>
+      <c r="Q37" s="14" t="n"/>
+      <c r="R37" s="14" t="n"/>
+      <c r="S37" s="14" t="n"/>
+      <c r="T37" s="14" t="n"/>
+      <c r="U37" s="14" t="n"/>
+      <c r="V37" s="14" t="n"/>
+      <c r="W37" s="14" t="n"/>
+      <c r="X37" s="4" t="n"/>
+      <c r="Y37" s="4" t="n"/>
+      <c r="Z37" s="13" t="n"/>
+      <c r="AA37" s="13" t="n"/>
+      <c r="AB37" s="4" t="n"/>
+      <c r="AC37" s="4" t="n"/>
+      <c r="AD37" s="4" t="n"/>
+      <c r="AE37" s="4" t="n"/>
+      <c r="AF37" s="4" t="n"/>
+      <c r="AG37" s="4" t="n"/>
+      <c r="AH37" s="4" t="n"/>
+      <c r="AI37" s="4" t="n"/>
+      <c r="AJ37" s="14" t="n"/>
+      <c r="AK37" s="14" t="n"/>
+      <c r="AL37" s="14" t="n"/>
+      <c r="AM37" s="14" t="n"/>
+      <c r="AN37" s="14" t="n"/>
+      <c r="AO37" s="14" t="n"/>
+      <c r="AP37" s="14" t="n"/>
+      <c r="AQ37" s="14" t="n"/>
+      <c r="AR37" s="14" t="n"/>
+      <c r="AS37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="11.1" customHeight="1" s="12">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="73" t="inlineStr">
         <is>
           <t>Руководитель</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="7" t="n"/>
-      <c r="N37" s="53" t="n"/>
-      <c r="O37" s="53" t="n"/>
-      <c r="P37" s="53" t="n"/>
-      <c r="Q37" s="53" t="n"/>
-      <c r="R37" s="53" t="n"/>
-      <c r="S37" s="53" t="n"/>
-      <c r="T37" s="53" t="n"/>
-      <c r="U37" s="53" t="n"/>
-      <c r="V37" s="53" t="n"/>
-      <c r="W37" s="53" t="n"/>
-      <c r="Z37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="74" t="n"/>
+      <c r="J38" s="74" t="n"/>
+      <c r="K38" s="74" t="n"/>
+      <c r="L38" s="74" t="n"/>
+      <c r="M38" s="74" t="n"/>
+      <c r="N38" s="74" t="n"/>
+      <c r="O38" s="74" t="n"/>
+      <c r="P38" s="74" t="n"/>
+      <c r="Q38" s="74" t="n"/>
+      <c r="R38" s="74" t="n"/>
+      <c r="S38" s="74" t="n"/>
+      <c r="T38" s="74" t="n"/>
+      <c r="U38" s="74" t="n"/>
+      <c r="V38" s="74" t="n"/>
+      <c r="W38" s="74" t="n"/>
+      <c r="X38" s="4" t="n"/>
+      <c r="Y38" s="4" t="n"/>
+      <c r="Z38" s="73" t="inlineStr">
         <is>
           <t>Бухгалтер</t>
         </is>
       </c>
-      <c r="AA37" s="4" t="n"/>
-      <c r="AG37" s="5" t="n"/>
-      <c r="AH37" s="5" t="n"/>
-      <c r="AI37" s="5" t="n"/>
-      <c r="AJ37" s="7" t="n"/>
-      <c r="AK37" s="53" t="n"/>
-      <c r="AL37" s="53" t="n"/>
-      <c r="AM37" s="53" t="n"/>
-      <c r="AN37" s="53" t="n"/>
-      <c r="AO37" s="53" t="n"/>
-      <c r="AP37" s="53" t="n"/>
-      <c r="AQ37" s="53" t="n"/>
-      <c r="AR37" s="53" t="n"/>
-    </row>
-    <row r="38" ht="11.1" customHeight="1"/>
+      <c r="AA38" s="4" t="n"/>
+      <c r="AB38" s="4" t="n"/>
+      <c r="AC38" s="4" t="n"/>
+      <c r="AD38" s="4" t="n"/>
+      <c r="AE38" s="4" t="n"/>
+      <c r="AF38" s="4" t="n"/>
+      <c r="AG38" s="74" t="n"/>
+      <c r="AH38" s="74" t="n"/>
+      <c r="AI38" s="74" t="n"/>
+      <c r="AJ38" s="74" t="n"/>
+      <c r="AK38" s="74" t="n"/>
+      <c r="AL38" s="74" t="n"/>
+      <c r="AM38" s="74" t="n"/>
+      <c r="AN38" s="74" t="n"/>
+      <c r="AO38" s="74" t="n"/>
+      <c r="AP38" s="74" t="n"/>
+      <c r="AQ38" s="74" t="n"/>
+      <c r="AR38" s="74" t="n"/>
+      <c r="AS38" s="74" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="B2:W3"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AD2:AR2"/>
-    <mergeCell ref="X3:AC4"/>
-    <mergeCell ref="AD3:AR4"/>
-    <mergeCell ref="B4:W4"/>
+  <mergeCells count="50">
+    <mergeCell ref="AL25:AQ25"/>
+    <mergeCell ref="AL26:AQ26"/>
+    <mergeCell ref="AL27:AQ27"/>
+    <mergeCell ref="AK22:AQ22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:X23"/>
+    <mergeCell ref="AF23:AJ23"/>
+    <mergeCell ref="AK23:AQ23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:X22"/>
+    <mergeCell ref="Y22:AB22"/>
+    <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="AF22:AJ22"/>
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="G14:AR15"/>
+    <mergeCell ref="B17:F18"/>
+    <mergeCell ref="G17:AR18"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G20:AR20"/>
     <mergeCell ref="AD5:AR8"/>
     <mergeCell ref="B6:W7"/>
     <mergeCell ref="B8:W8"/>
@@ -1756,33 +2000,12 @@
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="O5:W5"/>
     <mergeCell ref="X5:AC8"/>
-    <mergeCell ref="B14:F15"/>
-    <mergeCell ref="G14:AR15"/>
-    <mergeCell ref="B17:F18"/>
-    <mergeCell ref="G17:AR18"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G20:AR20"/>
-    <mergeCell ref="AK22:AQ22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:X23"/>
-    <mergeCell ref="AF23:AJ23"/>
-    <mergeCell ref="AK23:AQ23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:X22"/>
-    <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="AF22:AJ22"/>
-    <mergeCell ref="AL25:AQ25"/>
-    <mergeCell ref="AL26:AQ26"/>
-    <mergeCell ref="AL27:AQ27"/>
-    <mergeCell ref="B28:AR28"/>
-    <mergeCell ref="B29:AP29"/>
-    <mergeCell ref="B31:AR31"/>
-    <mergeCell ref="B32:AR32"/>
-    <mergeCell ref="B33:AR33"/>
-    <mergeCell ref="B34:AR34"/>
-    <mergeCell ref="M37:W37"/>
-    <mergeCell ref="AJ37:AR37"/>
+    <mergeCell ref="B2:W3"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AD2:AR2"/>
+    <mergeCell ref="X3:AC4"/>
+    <mergeCell ref="AD3:AR4"/>
+    <mergeCell ref="B4:W4"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="B24:C24"/>
@@ -1791,6 +2014,13 @@
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="AF24:AJ24"/>
     <mergeCell ref="AK24:AQ24"/>
+    <mergeCell ref="AL28:AQ28"/>
+    <mergeCell ref="B29:AR29"/>
+    <mergeCell ref="B30:AP30"/>
+    <mergeCell ref="B32:AQ32"/>
+    <mergeCell ref="B33:AQ33"/>
+    <mergeCell ref="B34:AQ34"/>
+    <mergeCell ref="B35:AQ35"/>
   </mergeCells>
   <pageMargins left="0.75" right="1" top="0.75" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
